--- a/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
+++ b/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="89">
   <si>
     <t>Total Hours</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Review SCT2 procedure</t>
+  </si>
+  <si>
+    <t>SCT-2: Develop Hydra for SCT-2</t>
   </si>
   <si>
     <t>Reverify Hydra-Li Comms</t>
@@ -418,10 +421,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="m\/d"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -469,20 +472,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Lato"/>
@@ -507,21 +496,57 @@
       <charset val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -535,7 +560,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -558,24 +583,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -590,35 +630,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -632,22 +652,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -655,11 +659,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -725,14 +728,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFBBC04"/>
+        <fgColor rgb="FFA6A6A6"/>
+        <bgColor rgb="FFB7B7B7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA6A6A6"/>
-        <bgColor rgb="FFB7B7B7"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFBBC04"/>
       </patternFill>
     </fill>
     <fill>
@@ -767,7 +770,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -779,7 +812,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -791,25 +890,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,73 +926,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -899,55 +950,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1031,30 +1034,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1213,19 +1192,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1285,17 +1251,57 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thick">
+        <color auto="1"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thick">
+        <color auto="1"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1317,8 +1323,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1348,13 +1356,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1373,154 +1385,145 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="42" borderId="35" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="44" borderId="36" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -1558,52 +1561,46 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1612,25 +1609,35 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="176" fontId="3" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="3" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1638,29 +1645,28 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1668,66 +1674,73 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2140,7 +2153,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB999"/>
+  <dimension ref="A1:AB1000"/>
   <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -2163,31 +2176,31 @@
         <v>0</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="58"/>
-      <c r="Z1" s="58"/>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="58"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="59"/>
+      <c r="Z1" s="59"/>
+      <c r="AA1" s="59"/>
+      <c r="AB1" s="59"/>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:28">
       <c r="A2" s="4"/>
@@ -2199,30 +2212,30 @@
       <c r="E2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="20">
         <v>46258</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="21">
         <f t="shared" ref="G2:V2" si="0">F2+7</f>
         <v>46265</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="22">
         <f t="shared" si="0"/>
         <v>46272</v>
       </c>
-      <c r="I2" s="37">
+      <c r="I2" s="35">
         <f t="shared" si="0"/>
         <v>46279</v>
       </c>
-      <c r="J2" s="38">
+      <c r="J2" s="36">
         <f t="shared" si="0"/>
         <v>46286</v>
       </c>
-      <c r="K2" s="39">
+      <c r="K2" s="37">
         <f t="shared" si="0"/>
         <v>46293</v>
       </c>
-      <c r="L2" s="38">
+      <c r="L2" s="36">
         <f t="shared" si="0"/>
         <v>46300</v>
       </c>
@@ -2230,23 +2243,23 @@
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-      <c r="N2" s="38">
+      <c r="N2" s="36">
         <f t="shared" si="0"/>
         <v>46314</v>
       </c>
-      <c r="O2" s="38">
+      <c r="O2" s="36">
         <f t="shared" si="0"/>
         <v>46321</v>
       </c>
-      <c r="P2" s="39">
+      <c r="P2" s="37">
         <f t="shared" si="0"/>
         <v>46328</v>
       </c>
-      <c r="Q2" s="38">
+      <c r="Q2" s="36">
         <f t="shared" si="0"/>
         <v>46335</v>
       </c>
-      <c r="R2" s="39">
+      <c r="R2" s="37">
         <f t="shared" si="0"/>
         <v>46342</v>
       </c>
@@ -2254,7 +2267,7 @@
         <f t="shared" si="0"/>
         <v>46349</v>
       </c>
-      <c r="T2" s="39">
+      <c r="T2" s="37">
         <f t="shared" si="0"/>
         <v>46356</v>
       </c>
@@ -2266,18 +2279,18 @@
         <f t="shared" si="0"/>
         <v>46370</v>
       </c>
-      <c r="W2" s="39"/>
-      <c r="X2" s="48" t="s">
+      <c r="W2" s="37"/>
+      <c r="X2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Y2" s="59" t="s">
+      <c r="Y2" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="Z2" s="59" t="s">
+      <c r="Z2" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
+      <c r="AA2" s="61"/>
+      <c r="AB2" s="61"/>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:28">
       <c r="A3" s="6" t="s">
@@ -2285,95 +2298,95 @@
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="7">
-        <f>D3/$D$64</f>
-        <v>0.318681318681319</v>
+        <f>D3/$D$65</f>
+        <v>0.31294964028777</v>
       </c>
       <c r="D3" s="8">
         <f>D4+D7+D11+D14</f>
         <v>87</v>
       </c>
-      <c r="E3" s="25">
-        <f t="shared" ref="E3:E63" si="1">SUM(F3:W3)</f>
+      <c r="E3" s="23">
+        <f t="shared" ref="E3:E64" si="1">SUM(F3:W3)</f>
         <v>48</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="24">
         <f t="shared" ref="F3:V3" si="2">F4+F7+F11+F14</f>
         <v>14</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="24">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="24">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="24">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="24">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T3" s="26">
+      <c r="T3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U3" s="26">
+      <c r="U3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V3" s="26">
+      <c r="V3" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W3" s="49"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="58"/>
-      <c r="Z3" s="61" t="s">
+      <c r="W3" s="51"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="59"/>
+      <c r="Z3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="AA3" s="62" t="s">
+      <c r="AA3" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="AB3" s="63"/>
+      <c r="AB3" s="64"/>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:28">
       <c r="A4" s="9"/>
@@ -2385,93 +2398,93 @@
         <f>SUM(D5:D6)</f>
         <v>35</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="25">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="26">
         <f t="shared" ref="F4:W4" si="3">SUM(F5:F6)</f>
         <v>3</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="26">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="26">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="26">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="26">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U4" s="28">
+      <c r="U4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V4" s="28">
+      <c r="V4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W4" s="36">
+      <c r="W4" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X4" s="51" t="s">
+      <c r="X4" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="64" t="s">
+      <c r="Y4" s="59"/>
+      <c r="Z4" s="65" t="s">
         <v>12</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="65" t="s">
+      <c r="AB4" s="66" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2484,49 +2497,49 @@
       <c r="D5" s="11">
         <v>15</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="25">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="27">
         <v>1</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="26">
         <v>1</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="26">
         <v>1</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="26">
         <v>1</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="26">
         <v>1</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="51" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="26"/>
+      <c r="X5" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Y5" s="58"/>
-      <c r="Z5" s="66" t="s">
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="AA5" s="67" t="s">
+      <c r="AA5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="AB5" s="63" t="s">
+      <c r="AB5" s="64" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2539,49 +2552,49 @@
       <c r="D6" s="17">
         <v>20</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="28">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="29">
         <v>2</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="30">
         <v>2</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="30">
         <v>2</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="30">
         <v>2</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="30">
         <v>2</v>
       </c>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="52" t="s">
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="Y6" s="58"/>
-      <c r="Z6" s="64" t="s">
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AA6" s="68" t="s">
+      <c r="AA6" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="AB6" s="58"/>
+      <c r="AB6" s="59"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:28">
       <c r="A7" s="9"/>
@@ -2593,93 +2606,93 @@
         <f>SUM(D8:D10)</f>
         <v>33</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="25">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="31">
         <f t="shared" ref="F7:W7" si="4">SUM(F8:F10)</f>
         <v>4</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="31">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="31">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="31">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="31">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M7" s="33">
+      <c r="M7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O7" s="33">
+      <c r="O7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P7" s="33">
+      <c r="P7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="33">
+      <c r="Q7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R7" s="33">
+      <c r="R7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S7" s="33">
+      <c r="S7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T7" s="33">
+      <c r="T7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="U7" s="33">
+      <c r="U7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V7" s="33">
+      <c r="V7" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W7" s="36">
+      <c r="W7" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="X7" s="51" t="s">
+      <c r="X7" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Y7" s="58"/>
-      <c r="Z7" s="64" t="s">
+      <c r="Y7" s="59"/>
+      <c r="Z7" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="AA7" s="69" t="s">
+      <c r="AA7" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="AB7" s="58"/>
+      <c r="AB7" s="59"/>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:28">
       <c r="A8" s="9"/>
@@ -2690,49 +2703,49 @@
       <c r="D8" s="11">
         <v>9</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="25">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="27">
         <v>1</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="26">
         <v>1</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="26">
         <v>1</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="26">
         <v>1</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="26">
         <v>1</v>
       </c>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="51" t="s">
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Y8" s="58"/>
-      <c r="Z8" s="64" t="s">
+      <c r="Y8" s="59"/>
+      <c r="Z8" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="AA8" s="70" t="s">
+      <c r="AA8" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="AB8" s="58"/>
+      <c r="AB8" s="59"/>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:28">
       <c r="A9" s="9"/>
@@ -2743,45 +2756,45 @@
       <c r="D9" s="11">
         <v>12</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="25">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="27">
         <v>1</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="26">
         <v>1</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="26">
         <v>1</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="26">
         <v>1</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="26">
         <v>1</v>
       </c>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="51" t="s">
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Y9" s="58"/>
-      <c r="Z9" s="71"/>
-      <c r="AA9" s="72"/>
-      <c r="AB9" s="58"/>
+      <c r="Y9" s="59"/>
+      <c r="Z9" s="72"/>
+      <c r="AA9" s="73"/>
+      <c r="AB9" s="59"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:28">
       <c r="A10" s="14"/>
@@ -2792,45 +2805,45 @@
       <c r="D10" s="17">
         <v>12</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="28">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="29">
         <v>2</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="30">
         <v>1</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="30">
         <v>1</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="30">
         <v>1</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="30">
         <v>3</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="32"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="52" t="s">
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="Y10" s="58"/>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="63"/>
-      <c r="AB10" s="58"/>
+      <c r="Y10" s="59"/>
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="64"/>
+      <c r="AB10" s="59"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:28">
       <c r="A11" s="9"/>
@@ -2842,93 +2855,93 @@
         <f>SUM(D12:D13)</f>
         <v>15</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="25">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="31">
         <f t="shared" ref="F11:W11" si="5">SUM(F12:F13)</f>
         <v>7</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="31">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="31">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="I11" s="33">
+      <c r="I11" s="31">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="33">
+      <c r="K11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="33">
+      <c r="L11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="33">
+      <c r="M11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="33">
+      <c r="O11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="33">
+      <c r="P11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="33">
+      <c r="Q11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R11" s="33">
+      <c r="R11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S11" s="33">
+      <c r="S11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T11" s="33">
+      <c r="T11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U11" s="33">
+      <c r="U11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V11" s="33">
+      <c r="V11" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W11" s="36">
+      <c r="W11" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X11" s="51" t="s">
+      <c r="X11" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Y11" s="58"/>
-      <c r="Z11" s="64" t="s">
+      <c r="Y11" s="59"/>
+      <c r="Z11" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="73" t="s">
+      <c r="AA11" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="AB11" s="58"/>
+      <c r="AB11" s="59"/>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:28">
       <c r="A12" s="9"/>
@@ -2939,41 +2952,41 @@
       <c r="D12" s="11">
         <v>3</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="25">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="27">
         <v>3</v>
       </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="28"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="28"/>
-      <c r="W12" s="28"/>
-      <c r="X12" s="51" t="s">
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Y12" s="58"/>
-      <c r="Z12" s="74" t="s">
+      <c r="Y12" s="59"/>
+      <c r="Z12" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="AA12" s="67" t="s">
+      <c r="AA12" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="AB12" s="58"/>
+      <c r="AB12" s="59"/>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:28">
       <c r="A13" s="14"/>
@@ -2984,47 +2997,47 @@
       <c r="D13" s="17">
         <v>12</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="28">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="29">
         <v>4</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="30">
         <v>2</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="30">
         <v>4</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="30">
         <v>2</v>
       </c>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="46"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="52" t="s">
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="Y13" s="58"/>
-      <c r="Z13" s="64" t="s">
+      <c r="Y13" s="59"/>
+      <c r="Z13" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AA13" s="75" t="s">
+      <c r="AA13" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="AB13" s="58"/>
+      <c r="AB13" s="59"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:28">
       <c r="A14" s="9"/>
@@ -3036,93 +3049,93 @@
         <f>SUM(D15:D16)</f>
         <v>4</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="31">
         <f t="shared" ref="F14:W14" si="6">SUM(F15:F16)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L14" s="33">
+      <c r="L14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M14" s="33">
+      <c r="M14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N14" s="33">
+      <c r="N14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O14" s="33">
+      <c r="O14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="33">
+      <c r="Q14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R14" s="33">
+      <c r="R14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S14" s="33">
+      <c r="S14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T14" s="33">
+      <c r="T14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U14" s="33">
+      <c r="U14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V14" s="33">
+      <c r="V14" s="31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W14" s="36">
+      <c r="W14" s="34">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X14" s="51" t="s">
+      <c r="X14" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y14" s="58"/>
-      <c r="Z14" s="64" t="s">
+      <c r="Y14" s="59"/>
+      <c r="Z14" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="AA14" s="76" t="s">
+      <c r="AA14" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="AB14" s="58"/>
+      <c r="AB14" s="59"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:28">
       <c r="A15" s="9"/>
@@ -3133,39 +3146,39 @@
       <c r="D15" s="11">
         <v>2</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
       <c r="M15" s="43"/>
-      <c r="N15" s="28"/>
+      <c r="N15" s="26"/>
       <c r="O15" s="44"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="28"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="28"/>
-      <c r="X15" s="51" t="s">
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y15" s="58"/>
-      <c r="Z15" s="64" t="s">
+      <c r="Y15" s="59"/>
+      <c r="Z15" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="AA15" s="69" t="s">
+      <c r="AA15" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="AB15" s="58"/>
+      <c r="AB15" s="59"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:28">
       <c r="A16" s="14"/>
@@ -3176,39 +3189,39 @@
       <c r="D16" s="17">
         <v>2</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="53"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="52" t="s">
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="55"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="Y16" s="58"/>
-      <c r="Z16" s="64" t="s">
+      <c r="Y16" s="59"/>
+      <c r="Z16" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="AA16" s="70" t="s">
+      <c r="AA16" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="AB16" s="58"/>
+      <c r="AB16" s="59"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:28">
       <c r="A17" s="18" t="s">
@@ -3216,90 +3229,90 @@
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="7">
-        <f>D17/$D$64</f>
-        <v>0.227106227106227</v>
+        <f>D17/$D$65</f>
+        <v>0.223021582733813</v>
       </c>
       <c r="D17" s="8">
         <f>D18+D21+D23+D26</f>
         <v>62</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="23">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="32">
         <f t="shared" ref="F17:V17" si="7">F18+F21+F23+F26</f>
         <v>1</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="32">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="32">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="I17" s="34">
+      <c r="I17" s="32">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="32">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="K17" s="34">
+      <c r="K17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M17" s="34">
+      <c r="M17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N17" s="34">
+      <c r="N17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O17" s="34">
+      <c r="O17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P17" s="34">
+      <c r="P17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="34">
+      <c r="Q17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R17" s="34">
+      <c r="R17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S17" s="34">
+      <c r="S17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T17" s="34">
+      <c r="T17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U17" s="34">
+      <c r="U17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="V17" s="34">
+      <c r="V17" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W17" s="54"/>
-      <c r="X17" s="55"/>
-      <c r="Y17" s="58"/>
-      <c r="AA17" s="77"/>
-      <c r="AB17" s="58"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="57"/>
+      <c r="Y17" s="59"/>
+      <c r="AA17" s="78"/>
+      <c r="AB17" s="59"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:28">
       <c r="A18" s="9"/>
@@ -3311,91 +3324,91 @@
         <f>SUM(D19:D20)</f>
         <v>4</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="25">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="31">
         <f t="shared" ref="F18:W18" si="8">SUM(F19:F20)</f>
         <v>1</v>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="31">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="H18" s="33">
+      <c r="H18" s="31">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="I18" s="33">
+      <c r="I18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J18" s="33">
+      <c r="J18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K18" s="33">
+      <c r="K18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L18" s="33">
+      <c r="L18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M18" s="33">
+      <c r="M18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N18" s="33">
+      <c r="N18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O18" s="33">
+      <c r="O18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P18" s="33">
+      <c r="P18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="33">
+      <c r="Q18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R18" s="33">
+      <c r="R18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S18" s="33">
+      <c r="S18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T18" s="33">
+      <c r="T18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U18" s="33">
+      <c r="U18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V18" s="33">
+      <c r="V18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W18" s="33">
+      <c r="W18" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X18" s="51" t="s">
+      <c r="X18" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Y18" s="58"/>
-      <c r="Z18" s="78" t="s">
+      <c r="Y18" s="59"/>
+      <c r="Z18" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="AA18" s="78"/>
-      <c r="AB18" s="58"/>
+      <c r="AA18" s="79"/>
+      <c r="AB18" s="59"/>
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:28">
       <c r="A19" s="9"/>
@@ -3406,41 +3419,41 @@
       <c r="D19" s="11">
         <v>2</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="25">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="26">
         <v>1</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="33">
         <v>1</v>
       </c>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="51" t="s">
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="26"/>
+      <c r="U19" s="26"/>
+      <c r="V19" s="26"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Y19" s="58"/>
-      <c r="Z19" s="79" t="s">
+      <c r="Y19" s="59"/>
+      <c r="Z19" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="AA19" s="79"/>
-      <c r="AB19" s="58"/>
+      <c r="AA19" s="80"/>
+      <c r="AB19" s="59"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:28">
       <c r="A20" s="14"/>
@@ -3451,39 +3464,39 @@
       <c r="D20" s="17">
         <v>2</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="28">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="32">
+      <c r="F20" s="29"/>
+      <c r="G20" s="30">
         <v>1</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="33">
         <v>1</v>
       </c>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="46"/>
-      <c r="T20" s="32"/>
-      <c r="U20" s="32"/>
-      <c r="V20" s="32"/>
-      <c r="W20" s="32"/>
-      <c r="X20" s="52" t="s">
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="Y20" s="58"/>
-      <c r="Z20" s="79"/>
-      <c r="AA20" s="79"/>
-      <c r="AB20" s="58"/>
+      <c r="Y20" s="59"/>
+      <c r="Z20" s="80"/>
+      <c r="AA20" s="80"/>
+      <c r="AB20" s="59"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:28">
       <c r="A21" s="9"/>
@@ -3494,91 +3507,91 @@
       <c r="D21" s="11">
         <v>6</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="25">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="31">
         <f t="shared" ref="F21:W21" si="9">SUM(F22)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="31">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="31">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="31">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="K21" s="33">
+      <c r="K21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="V21" s="33">
+      <c r="V21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W21" s="33">
+      <c r="W21" s="31">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X21" s="51" t="s">
+      <c r="X21" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y21" s="58"/>
-      <c r="Z21" s="80" t="s">
+      <c r="Y21" s="59"/>
+      <c r="Z21" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="58"/>
+      <c r="AA21" s="81"/>
+      <c r="AB21" s="59"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:28">
       <c r="A22" s="9"/>
@@ -3589,41 +3602,41 @@
       <c r="D22" s="11">
         <v>6</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="25">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F22" s="29"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28">
+      <c r="F22" s="27"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26">
         <v>1</v>
       </c>
-      <c r="I22" s="28">
+      <c r="I22" s="26">
         <v>1</v>
       </c>
-      <c r="J22" s="28">
+      <c r="J22" s="26">
         <v>1</v>
       </c>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="45"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="28"/>
-      <c r="W22" s="28"/>
-      <c r="X22" s="51" t="s">
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="26"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y22" s="58"/>
-      <c r="Z22" s="80"/>
-      <c r="AA22" s="80"/>
-      <c r="AB22" s="58"/>
+      <c r="Y22" s="59"/>
+      <c r="Z22" s="81"/>
+      <c r="AA22" s="81"/>
+      <c r="AB22" s="59"/>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:28">
       <c r="A23" s="9"/>
@@ -3635,56 +3648,56 @@
         <f>SUM(D24:D25)</f>
         <v>15</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="31">
         <f t="shared" ref="F23:K23" si="10">SUM(F24:F25)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J23" s="36">
+      <c r="J23" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="34">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="36"/>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36">
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="47"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="34"/>
+      <c r="W23" s="34">
         <f>SUM(W24:W25)</f>
         <v>0</v>
       </c>
-      <c r="X23" s="51" t="s">
+      <c r="X23" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y23" s="58"/>
-      <c r="Z23" s="58"/>
-      <c r="AA23" s="58"/>
-      <c r="AB23" s="58"/>
+      <c r="Y23" s="59"/>
+      <c r="Z23" s="59"/>
+      <c r="AA23" s="59"/>
+      <c r="AB23" s="59"/>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:28">
       <c r="A24" s="9"/>
@@ -3695,35 +3708,35 @@
       <c r="D24" s="11">
         <v>5</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F24" s="29"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="28"/>
-      <c r="X24" s="51" t="s">
+      <c r="F24" s="27"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="47"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="26"/>
+      <c r="W24" s="26"/>
+      <c r="X24" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y24" s="58"/>
-      <c r="Z24" s="58"/>
-      <c r="AA24" s="58"/>
-      <c r="AB24" s="58"/>
+      <c r="Y24" s="59"/>
+      <c r="Z24" s="59"/>
+      <c r="AA24" s="59"/>
+      <c r="AB24" s="59"/>
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:28">
       <c r="A25" s="14"/>
@@ -3734,35 +3747,35 @@
       <c r="D25" s="17">
         <v>10</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="32"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="46"/>
-      <c r="T25" s="32"/>
-      <c r="U25" s="40"/>
-      <c r="V25" s="32"/>
-      <c r="W25" s="32"/>
-      <c r="X25" s="52" t="s">
+      <c r="F25" s="29"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="48"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="Y25" s="58"/>
-      <c r="Z25" s="58"/>
-      <c r="AA25" s="58"/>
-      <c r="AB25" s="58"/>
+      <c r="Y25" s="59"/>
+      <c r="Z25" s="59"/>
+      <c r="AA25" s="59"/>
+      <c r="AB25" s="59"/>
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:28">
       <c r="A26" s="9"/>
@@ -3774,56 +3787,56 @@
         <f>SUM(D27:D28)</f>
         <v>37</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="31">
         <f t="shared" ref="F26:K26" si="11">SUM(F27:F28)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="34">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="34">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I26" s="36">
+      <c r="I26" s="34">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J26" s="36">
+      <c r="J26" s="34">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="34">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="36">
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="47"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="26"/>
+      <c r="W26" s="34">
         <f>SUM(W27:W28)</f>
         <v>0</v>
       </c>
-      <c r="X26" s="51" t="s">
+      <c r="X26" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y26" s="58"/>
-      <c r="Z26" s="58"/>
-      <c r="AA26" s="58"/>
-      <c r="AB26" s="58"/>
+      <c r="Y26" s="59"/>
+      <c r="Z26" s="59"/>
+      <c r="AA26" s="59"/>
+      <c r="AB26" s="59"/>
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:28">
       <c r="A27" s="9"/>
@@ -3834,35 +3847,35 @@
       <c r="D27" s="11">
         <v>15</v>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F27" s="29"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="28"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="51" t="s">
+      <c r="F27" s="27"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="40"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="26"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y27" s="58"/>
-      <c r="Z27" s="58"/>
-      <c r="AA27" s="58"/>
-      <c r="AB27" s="58"/>
+      <c r="Y27" s="59"/>
+      <c r="Z27" s="59"/>
+      <c r="AA27" s="59"/>
+      <c r="AB27" s="59"/>
     </row>
     <row r="28" ht="18.75" customHeight="1" spans="1:28">
       <c r="A28" s="14"/>
@@ -3873,35 +3886,35 @@
       <c r="D28" s="17">
         <v>22</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="40"/>
-      <c r="W28" s="32"/>
-      <c r="X28" s="52" t="s">
+      <c r="F28" s="29"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="Y28" s="58"/>
-      <c r="Z28" s="58"/>
-      <c r="AA28" s="58"/>
-      <c r="AB28" s="58"/>
+      <c r="Y28" s="59"/>
+      <c r="Z28" s="59"/>
+      <c r="AA28" s="59"/>
+      <c r="AB28" s="59"/>
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:28">
       <c r="A29" s="18" t="s">
@@ -3909,91 +3922,91 @@
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="7">
-        <f>D29/$D$64</f>
-        <v>0.454212454212454</v>
+        <f>D29/$D$65</f>
+        <v>0.464028776978417</v>
       </c>
       <c r="D29" s="8">
-        <f>D30+D40+D47+D52+D61</f>
-        <v>124</v>
-      </c>
-      <c r="E29" s="25">
+        <f>D30+D40+D47+D52+D62</f>
+        <v>129</v>
+      </c>
+      <c r="E29" s="23">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="F29" s="34">
-        <f t="shared" ref="F29:V29" si="12">F30+F40+F47+F52+F61</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="34">
+        <v>22</v>
+      </c>
+      <c r="F29" s="32">
+        <f t="shared" ref="F29:V29" si="12">F30+F40+F47+F52+F62</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="32">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="32">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="I29" s="34">
+      <c r="I29" s="32">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="J29" s="34">
+      <c r="J29" s="32">
         <f t="shared" si="12"/>
         <v>8</v>
       </c>
-      <c r="K29" s="34">
+      <c r="K29" s="32">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="34">
+        <v>2</v>
+      </c>
+      <c r="L29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M29" s="34">
+      <c r="M29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="N29" s="34">
+      <c r="N29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O29" s="34">
+      <c r="O29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="P29" s="34">
+      <c r="P29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="34">
+      <c r="Q29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R29" s="34">
+      <c r="R29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S29" s="34">
+      <c r="S29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T29" s="34">
+      <c r="T29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U29" s="34">
+      <c r="U29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="V29" s="34">
+      <c r="V29" s="32">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="W29" s="54"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="58"/>
-      <c r="Z29" s="58"/>
-      <c r="AA29" s="58"/>
-      <c r="AB29" s="58"/>
+      <c r="W29" s="56"/>
+      <c r="X29" s="57"/>
+      <c r="Y29" s="59"/>
+      <c r="Z29" s="59"/>
+      <c r="AA29" s="59"/>
+      <c r="AB29" s="59"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" spans="1:28">
       <c r="A30" s="9"/>
@@ -4005,89 +4018,89 @@
         <f>SUM(D31:D39)</f>
         <v>26</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="25">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="F30" s="33">
+        <v>9</v>
+      </c>
+      <c r="F30" s="31">
         <f t="shared" ref="F30:W30" si="13">SUM(F31:F39)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="34">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="34">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="34">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="34">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="36">
+        <v>2</v>
+      </c>
+      <c r="L30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="P30" s="36">
+      <c r="P30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U30" s="36">
+      <c r="U30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X30" s="51" t="s">
+      <c r="X30" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y30" s="58"/>
-      <c r="Z30" s="58"/>
-      <c r="AA30" s="58"/>
-      <c r="AB30" s="58"/>
+      <c r="Y30" s="59"/>
+      <c r="Z30" s="59"/>
+      <c r="AA30" s="59"/>
+      <c r="AB30" s="59"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:28">
       <c r="A31" s="9"/>
@@ -4098,41 +4111,41 @@
       <c r="D31" s="11">
         <v>1</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="25">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F31" s="29"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28">
+      <c r="F31" s="27"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26">
         <v>1</v>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="38">
         <v>1</v>
       </c>
-      <c r="J31" s="28">
+      <c r="J31" s="26">
         <v>2</v>
       </c>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="28"/>
-      <c r="V31" s="28"/>
-      <c r="W31" s="28"/>
-      <c r="X31" s="56" t="s">
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="47"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="26"/>
+      <c r="W31" s="26"/>
+      <c r="X31" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="Y31" s="58"/>
-      <c r="Z31" s="58"/>
-      <c r="AA31" s="58"/>
-      <c r="AB31" s="58"/>
+      <c r="Y31" s="59"/>
+      <c r="Z31" s="59"/>
+      <c r="AA31" s="59"/>
+      <c r="AB31" s="59"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:28">
       <c r="A32" s="9"/>
@@ -4143,39 +4156,39 @@
       <c r="D32" s="11">
         <v>2</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="25">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F32" s="29"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="40">
+      <c r="F32" s="27"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="39">
         <v>1</v>
       </c>
-      <c r="J32" s="28">
+      <c r="J32" s="26">
         <v>2</v>
       </c>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="56" t="s">
+      <c r="K32" s="40"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="47"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="26"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="Y32" s="58"/>
-      <c r="Z32" s="58"/>
-      <c r="AA32" s="58"/>
-      <c r="AB32" s="58"/>
+      <c r="Y32" s="59"/>
+      <c r="Z32" s="59"/>
+      <c r="AA32" s="59"/>
+      <c r="AB32" s="59"/>
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:28">
       <c r="A33" s="9"/>
@@ -4186,33 +4199,35 @@
       <c r="D33" s="11">
         <v>4</v>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="29"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
-      <c r="V33" s="28"/>
-      <c r="W33" s="28"/>
-      <c r="X33" s="56"/>
-      <c r="Y33" s="58"/>
-      <c r="Z33" s="58"/>
-      <c r="AA33" s="58"/>
-      <c r="AB33" s="58"/>
+        <v>2</v>
+      </c>
+      <c r="F33" s="27"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="40">
+        <v>2</v>
+      </c>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="47"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="26"/>
+      <c r="W33" s="26"/>
+      <c r="X33" s="58"/>
+      <c r="Y33" s="59"/>
+      <c r="Z33" s="59"/>
+      <c r="AA33" s="59"/>
+      <c r="AB33" s="59"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:28">
       <c r="A34" s="9"/>
@@ -4223,33 +4238,33 @@
       <c r="D34" s="11">
         <v>4</v>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F34" s="29"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
-      <c r="V34" s="28"/>
-      <c r="W34" s="28"/>
-      <c r="X34" s="56"/>
-      <c r="Y34" s="58"/>
-      <c r="Z34" s="58"/>
-      <c r="AA34" s="58"/>
-      <c r="AB34" s="58"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="47"/>
+      <c r="T34" s="26"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="26"/>
+      <c r="W34" s="26"/>
+      <c r="X34" s="58"/>
+      <c r="Y34" s="59"/>
+      <c r="Z34" s="59"/>
+      <c r="AA34" s="59"/>
+      <c r="AB34" s="59"/>
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:28">
       <c r="A35" s="9"/>
@@ -4260,33 +4275,33 @@
       <c r="D35" s="11">
         <v>4</v>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F35" s="29"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="45"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
-      <c r="V35" s="28"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="56"/>
-      <c r="Y35" s="58"/>
-      <c r="Z35" s="58"/>
-      <c r="AA35" s="58"/>
-      <c r="AB35" s="58"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="26"/>
+      <c r="S35" s="47"/>
+      <c r="T35" s="26"/>
+      <c r="U35" s="26"/>
+      <c r="V35" s="26"/>
+      <c r="W35" s="26"/>
+      <c r="X35" s="58"/>
+      <c r="Y35" s="59"/>
+      <c r="Z35" s="59"/>
+      <c r="AA35" s="59"/>
+      <c r="AB35" s="59"/>
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:28">
       <c r="A36" s="9"/>
@@ -4297,33 +4312,33 @@
       <c r="D36" s="11">
         <v>4</v>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F36" s="29"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="45"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="56"/>
-      <c r="Y36" s="58"/>
-      <c r="Z36" s="58"/>
-      <c r="AA36" s="58"/>
-      <c r="AB36" s="58"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="47"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="26"/>
+      <c r="W36" s="26"/>
+      <c r="X36" s="58"/>
+      <c r="Y36" s="59"/>
+      <c r="Z36" s="59"/>
+      <c r="AA36" s="59"/>
+      <c r="AB36" s="59"/>
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:28">
       <c r="A37" s="9"/>
@@ -4334,35 +4349,35 @@
       <c r="D37" s="11">
         <v>2</v>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F37" s="29"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="56" t="s">
+      <c r="F37" s="27"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
+      <c r="S37" s="47"/>
+      <c r="T37" s="26"/>
+      <c r="U37" s="26"/>
+      <c r="V37" s="26"/>
+      <c r="W37" s="26"/>
+      <c r="X37" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="Y37" s="58"/>
-      <c r="Z37" s="58"/>
-      <c r="AA37" s="58"/>
-      <c r="AB37" s="58"/>
+      <c r="Y37" s="59"/>
+      <c r="Z37" s="59"/>
+      <c r="AA37" s="59"/>
+      <c r="AB37" s="59"/>
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:28">
       <c r="A38" s="9"/>
@@ -4373,35 +4388,35 @@
       <c r="D38" s="11">
         <v>3</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F38" s="29"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="45"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="56" t="s">
+      <c r="F38" s="27"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+      <c r="S38" s="47"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26"/>
+      <c r="V38" s="26"/>
+      <c r="W38" s="26"/>
+      <c r="X38" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="Y38" s="58"/>
-      <c r="Z38" s="58"/>
-      <c r="AA38" s="58"/>
-      <c r="AB38" s="58"/>
+      <c r="Y38" s="59"/>
+      <c r="Z38" s="59"/>
+      <c r="AA38" s="59"/>
+      <c r="AB38" s="59"/>
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:28">
       <c r="A39" s="9"/>
@@ -4412,35 +4427,35 @@
       <c r="D39" s="11">
         <v>2</v>
       </c>
-      <c r="E39" s="27">
+      <c r="E39" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F39" s="29"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="45"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="56" t="s">
+      <c r="F39" s="27"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26"/>
+      <c r="S39" s="47"/>
+      <c r="T39" s="26"/>
+      <c r="U39" s="26"/>
+      <c r="V39" s="26"/>
+      <c r="W39" s="26"/>
+      <c r="X39" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="Y39" s="58"/>
-      <c r="Z39" s="58"/>
-      <c r="AA39" s="58"/>
-      <c r="AB39" s="58"/>
+      <c r="Y39" s="59"/>
+      <c r="Z39" s="59"/>
+      <c r="AA39" s="59"/>
+      <c r="AB39" s="59"/>
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:28">
       <c r="A40" s="9"/>
@@ -4452,89 +4467,89 @@
         <f>SUM(D41:D46)</f>
         <v>15</v>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F40" s="33">
+      <c r="F40" s="31">
         <f t="shared" ref="F40:W40" si="14">SUM(F41:F46)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="36">
+      <c r="G40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H40" s="36">
+      <c r="H40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I40" s="36">
+      <c r="I40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J40" s="36">
+      <c r="J40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K40" s="36">
+      <c r="K40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L40" s="36">
+      <c r="L40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M40" s="36">
+      <c r="M40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N40" s="36">
+      <c r="N40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O40" s="36">
+      <c r="O40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="P40" s="36">
+      <c r="P40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Q40" s="36">
+      <c r="Q40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R40" s="36">
+      <c r="R40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S40" s="36">
+      <c r="S40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="T40" s="36">
+      <c r="T40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="U40" s="36">
+      <c r="U40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="V40" s="36">
+      <c r="V40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W40" s="36">
+      <c r="W40" s="34">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="X40" s="51" t="s">
+      <c r="X40" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y40" s="58"/>
-      <c r="Z40" s="58"/>
-      <c r="AA40" s="58"/>
-      <c r="AB40" s="58"/>
+      <c r="Y40" s="59"/>
+      <c r="Z40" s="59"/>
+      <c r="AA40" s="59"/>
+      <c r="AB40" s="59"/>
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:28">
       <c r="A41" s="9"/>
@@ -4545,35 +4560,35 @@
       <c r="D41" s="11">
         <v>1</v>
       </c>
-      <c r="E41" s="27">
+      <c r="E41" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F41" s="29"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="45"/>
-      <c r="T41" s="28"/>
-      <c r="U41" s="28"/>
-      <c r="V41" s="28"/>
-      <c r="W41" s="28"/>
-      <c r="X41" s="56" t="s">
+      <c r="F41" s="27"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="26"/>
+      <c r="S41" s="47"/>
+      <c r="T41" s="26"/>
+      <c r="U41" s="26"/>
+      <c r="V41" s="26"/>
+      <c r="W41" s="26"/>
+      <c r="X41" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="Y41" s="58"/>
-      <c r="Z41" s="58"/>
-      <c r="AA41" s="58"/>
-      <c r="AB41" s="58"/>
+      <c r="Y41" s="59"/>
+      <c r="Z41" s="59"/>
+      <c r="AA41" s="59"/>
+      <c r="AB41" s="59"/>
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:28">
       <c r="A42" s="9"/>
@@ -4584,35 +4599,35 @@
       <c r="D42" s="11">
         <v>2</v>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F42" s="29"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="28"/>
-      <c r="S42" s="45"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="28"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="28"/>
-      <c r="X42" s="56" t="s">
+      <c r="F42" s="27"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="40"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="47"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="26"/>
+      <c r="V42" s="26"/>
+      <c r="W42" s="26"/>
+      <c r="X42" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="Y42" s="58"/>
-      <c r="Z42" s="58"/>
-      <c r="AA42" s="58"/>
-      <c r="AB42" s="58"/>
+      <c r="Y42" s="59"/>
+      <c r="Z42" s="59"/>
+      <c r="AA42" s="59"/>
+      <c r="AB42" s="59"/>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:28">
       <c r="A43" s="9"/>
@@ -4623,33 +4638,33 @@
       <c r="D43" s="11">
         <v>5</v>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F43" s="29"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="45"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="28"/>
-      <c r="X43" s="56"/>
-      <c r="Y43" s="58"/>
-      <c r="Z43" s="58"/>
-      <c r="AA43" s="58"/>
-      <c r="AB43" s="58"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="40"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="47"/>
+      <c r="T43" s="26"/>
+      <c r="U43" s="26"/>
+      <c r="V43" s="26"/>
+      <c r="W43" s="26"/>
+      <c r="X43" s="58"/>
+      <c r="Y43" s="59"/>
+      <c r="Z43" s="59"/>
+      <c r="AA43" s="59"/>
+      <c r="AB43" s="59"/>
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:28">
       <c r="A44" s="9"/>
@@ -4660,35 +4675,35 @@
       <c r="D44" s="11">
         <v>2</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F44" s="29"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="28"/>
-      <c r="S44" s="45"/>
-      <c r="T44" s="28"/>
-      <c r="U44" s="28"/>
-      <c r="V44" s="28"/>
-      <c r="W44" s="28"/>
-      <c r="X44" s="56" t="s">
+      <c r="F44" s="27"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="39"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="40"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="26"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="47"/>
+      <c r="T44" s="26"/>
+      <c r="U44" s="26"/>
+      <c r="V44" s="26"/>
+      <c r="W44" s="26"/>
+      <c r="X44" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="Y44" s="58"/>
-      <c r="Z44" s="58"/>
-      <c r="AA44" s="58"/>
-      <c r="AB44" s="58"/>
+      <c r="Y44" s="59"/>
+      <c r="Z44" s="59"/>
+      <c r="AA44" s="59"/>
+      <c r="AB44" s="59"/>
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:28">
       <c r="A45" s="9"/>
@@ -4699,35 +4714,35 @@
       <c r="D45" s="11">
         <v>3</v>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F45" s="29"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="28"/>
-      <c r="O45" s="28"/>
-      <c r="P45" s="28"/>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="28"/>
-      <c r="S45" s="45"/>
-      <c r="T45" s="28"/>
-      <c r="U45" s="28"/>
-      <c r="V45" s="28"/>
-      <c r="W45" s="28"/>
-      <c r="X45" s="56" t="s">
+      <c r="F45" s="27"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="26"/>
+      <c r="P45" s="26"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="26"/>
+      <c r="S45" s="47"/>
+      <c r="T45" s="26"/>
+      <c r="U45" s="26"/>
+      <c r="V45" s="26"/>
+      <c r="W45" s="26"/>
+      <c r="X45" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="Y45" s="58"/>
-      <c r="Z45" s="58"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="58"/>
+      <c r="Y45" s="59"/>
+      <c r="Z45" s="59"/>
+      <c r="AA45" s="59"/>
+      <c r="AB45" s="59"/>
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:28">
       <c r="A46" s="14"/>
@@ -4738,35 +4753,35 @@
       <c r="D46" s="17">
         <v>2</v>
       </c>
-      <c r="E46" s="30">
+      <c r="E46" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F46" s="31"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
       <c r="K46" s="41"/>
-      <c r="L46" s="32"/>
-      <c r="M46" s="32"/>
-      <c r="N46" s="32"/>
-      <c r="O46" s="32"/>
-      <c r="P46" s="32"/>
-      <c r="Q46" s="32"/>
-      <c r="R46" s="32"/>
-      <c r="S46" s="46"/>
-      <c r="T46" s="32"/>
-      <c r="U46" s="32"/>
-      <c r="V46" s="32"/>
-      <c r="W46" s="32"/>
-      <c r="X46" s="52" t="s">
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="46"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="48"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="Y46" s="58"/>
-      <c r="Z46" s="58"/>
-      <c r="AA46" s="58"/>
-      <c r="AB46" s="58"/>
+      <c r="Y46" s="59"/>
+      <c r="Z46" s="59"/>
+      <c r="AA46" s="59"/>
+      <c r="AB46" s="59"/>
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:28">
       <c r="A47" s="9"/>
@@ -4778,89 +4793,89 @@
         <f>SUM(D48:D51)</f>
         <v>31</v>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="25">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F47" s="33">
+      <c r="F47" s="31">
         <f t="shared" ref="F47:W47" si="15">SUM(F48:F51)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="36">
+      <c r="G47" s="34">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="H47" s="36">
+      <c r="H47" s="34">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="I47" s="36">
+      <c r="I47" s="34">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="J47" s="36">
+      <c r="J47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K47" s="36">
+      <c r="K47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L47" s="36">
+      <c r="L47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="M47" s="36">
+      <c r="M47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N47" s="36">
+      <c r="N47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="O47" s="36">
+      <c r="O47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="P47" s="36">
+      <c r="P47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="36">
+      <c r="Q47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="R47" s="36">
+      <c r="R47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="S47" s="36">
+      <c r="S47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="T47" s="36">
+      <c r="T47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="U47" s="36">
+      <c r="U47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="V47" s="36">
+      <c r="V47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="W47" s="36">
+      <c r="W47" s="34">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="X47" s="51" t="s">
+      <c r="X47" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y47" s="58"/>
-      <c r="Z47" s="58"/>
-      <c r="AA47" s="58"/>
-      <c r="AB47" s="58"/>
+      <c r="Y47" s="59"/>
+      <c r="Z47" s="59"/>
+      <c r="AA47" s="59"/>
+      <c r="AB47" s="59"/>
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:28">
       <c r="A48" s="9"/>
@@ -4871,37 +4886,37 @@
       <c r="D48" s="11">
         <v>8</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="25">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F48" s="29"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28">
+      <c r="F48" s="27"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26">
         <v>1</v>
       </c>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
-      <c r="M48" s="40"/>
-      <c r="N48" s="28"/>
-      <c r="O48" s="28"/>
-      <c r="P48" s="28"/>
-      <c r="Q48" s="28"/>
-      <c r="R48" s="28"/>
-      <c r="S48" s="45"/>
-      <c r="T48" s="28"/>
-      <c r="U48" s="28"/>
-      <c r="V48" s="28"/>
-      <c r="W48" s="28"/>
-      <c r="X48" s="51" t="s">
+      <c r="J48" s="26"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="38"/>
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="26"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="26"/>
+      <c r="S48" s="47"/>
+      <c r="T48" s="26"/>
+      <c r="U48" s="26"/>
+      <c r="V48" s="26"/>
+      <c r="W48" s="26"/>
+      <c r="X48" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Y48" s="58"/>
-      <c r="Z48" s="58"/>
-      <c r="AA48" s="58"/>
-      <c r="AB48" s="58"/>
+      <c r="Y48" s="59"/>
+      <c r="Z48" s="59"/>
+      <c r="AA48" s="59"/>
+      <c r="AB48" s="59"/>
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:28">
       <c r="A49" s="9"/>
@@ -4912,35 +4927,35 @@
       <c r="D49" s="11">
         <v>5</v>
       </c>
-      <c r="E49" s="27">
+      <c r="E49" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F49" s="29"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="40"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="45"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="28"/>
-      <c r="V49" s="28"/>
-      <c r="W49" s="28"/>
-      <c r="X49" s="51" t="s">
+      <c r="F49" s="27"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="38"/>
+      <c r="N49" s="26"/>
+      <c r="O49" s="26"/>
+      <c r="P49" s="26"/>
+      <c r="Q49" s="26"/>
+      <c r="R49" s="26"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="26"/>
+      <c r="U49" s="26"/>
+      <c r="V49" s="26"/>
+      <c r="W49" s="26"/>
+      <c r="X49" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y49" s="58"/>
-      <c r="Z49" s="58"/>
-      <c r="AA49" s="58"/>
-      <c r="AB49" s="58"/>
+      <c r="Y49" s="59"/>
+      <c r="Z49" s="59"/>
+      <c r="AA49" s="59"/>
+      <c r="AB49" s="59"/>
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:28">
       <c r="A50" s="9"/>
@@ -4951,35 +4966,35 @@
       <c r="D50" s="11">
         <v>8</v>
       </c>
-      <c r="E50" s="27">
+      <c r="E50" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F50" s="29"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="28"/>
-      <c r="J50" s="28"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
-      <c r="M50" s="40"/>
-      <c r="N50" s="28"/>
-      <c r="O50" s="28"/>
-      <c r="P50" s="28"/>
-      <c r="Q50" s="28"/>
-      <c r="R50" s="28"/>
-      <c r="S50" s="45"/>
-      <c r="T50" s="28"/>
-      <c r="U50" s="28"/>
-      <c r="V50" s="28"/>
-      <c r="W50" s="28"/>
-      <c r="X50" s="51" t="s">
+      <c r="F50" s="27"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="26"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="39"/>
+      <c r="N50" s="40"/>
+      <c r="O50" s="26"/>
+      <c r="P50" s="26"/>
+      <c r="Q50" s="26"/>
+      <c r="R50" s="26"/>
+      <c r="S50" s="47"/>
+      <c r="T50" s="26"/>
+      <c r="U50" s="26"/>
+      <c r="V50" s="26"/>
+      <c r="W50" s="26"/>
+      <c r="X50" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y50" s="58"/>
-      <c r="Z50" s="58"/>
-      <c r="AA50" s="58"/>
-      <c r="AB50" s="58"/>
+      <c r="Y50" s="59"/>
+      <c r="Z50" s="59"/>
+      <c r="AA50" s="59"/>
+      <c r="AB50" s="59"/>
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:28">
       <c r="A51" s="14"/>
@@ -4990,39 +5005,39 @@
       <c r="D51" s="17">
         <v>10</v>
       </c>
-      <c r="E51" s="30">
+      <c r="E51" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F51" s="31"/>
-      <c r="G51" s="32">
+      <c r="F51" s="29"/>
+      <c r="G51" s="30">
         <v>2</v>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="30">
         <v>2</v>
       </c>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
       <c r="N51" s="41"/>
-      <c r="O51" s="32"/>
-      <c r="P51" s="32"/>
-      <c r="Q51" s="32"/>
-      <c r="R51" s="32"/>
-      <c r="S51" s="46"/>
-      <c r="T51" s="32"/>
-      <c r="U51" s="32"/>
-      <c r="V51" s="32"/>
-      <c r="W51" s="32"/>
-      <c r="X51" s="52" t="s">
+      <c r="O51" s="46"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="S51" s="48"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="30"/>
+      <c r="X51" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="Y51" s="58"/>
-      <c r="Z51" s="58"/>
-      <c r="AA51" s="58"/>
-      <c r="AB51" s="58"/>
+      <c r="Y51" s="59"/>
+      <c r="Z51" s="59"/>
+      <c r="AA51" s="59"/>
+      <c r="AB51" s="59"/>
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:28">
       <c r="A52" s="9"/>
@@ -5031,92 +5046,92 @@
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="11">
-        <f>SUM(D53:D60)</f>
-        <v>32</v>
-      </c>
-      <c r="E52" s="27">
+        <f>SUM(D53:D61)</f>
+        <v>37</v>
+      </c>
+      <c r="E52" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F52" s="33">
-        <f t="shared" ref="F52:W52" si="16">SUM(F53:F60)</f>
-        <v>0</v>
-      </c>
-      <c r="G52" s="36">
+      <c r="F52" s="31">
+        <f t="shared" ref="F52:W52" si="16">SUM(F53:F61)</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H52" s="36">
+      <c r="H52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I52" s="36">
+      <c r="I52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J52" s="36">
+      <c r="J52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K52" s="36">
+      <c r="K52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L52" s="36">
+      <c r="L52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M52" s="36">
+      <c r="M52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="N52" s="36">
+      <c r="N52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O52" s="36">
+      <c r="O52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="P52" s="28">
+      <c r="P52" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q52" s="36">
+      <c r="Q52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="R52" s="28">
+      <c r="R52" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="S52" s="45">
+      <c r="S52" s="47">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="T52" s="28">
+      <c r="T52" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="U52" s="28">
+      <c r="U52" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="V52" s="28">
+      <c r="V52" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="W52" s="36">
+      <c r="W52" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X52" s="51" t="s">
+      <c r="X52" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y52" s="58"/>
-      <c r="Z52" s="58"/>
-      <c r="AA52" s="58"/>
-      <c r="AB52" s="58"/>
+      <c r="Y52" s="59"/>
+      <c r="Z52" s="59"/>
+      <c r="AA52" s="59"/>
+      <c r="AB52" s="59"/>
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:28">
       <c r="A53" s="9"/>
@@ -5127,35 +5142,35 @@
       <c r="D53" s="11">
         <v>2</v>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F53" s="29"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
-      <c r="Q53" s="28"/>
-      <c r="R53" s="28"/>
-      <c r="S53" s="45"/>
-      <c r="T53" s="28"/>
-      <c r="U53" s="28"/>
-      <c r="V53" s="28"/>
-      <c r="W53" s="28"/>
-      <c r="X53" s="51" t="s">
+      <c r="F53" s="27"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="26"/>
+      <c r="K53" s="26"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="26"/>
+      <c r="O53" s="40"/>
+      <c r="P53" s="26"/>
+      <c r="Q53" s="26"/>
+      <c r="R53" s="26"/>
+      <c r="S53" s="47"/>
+      <c r="T53" s="26"/>
+      <c r="U53" s="26"/>
+      <c r="V53" s="26"/>
+      <c r="W53" s="26"/>
+      <c r="X53" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y53" s="58"/>
-      <c r="Z53" s="58"/>
-      <c r="AA53" s="58"/>
-      <c r="AB53" s="58"/>
+      <c r="Y53" s="59"/>
+      <c r="Z53" s="59"/>
+      <c r="AA53" s="59"/>
+      <c r="AB53" s="59"/>
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:28">
       <c r="A54" s="9"/>
@@ -5166,35 +5181,35 @@
       <c r="D54" s="11">
         <v>5</v>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F54" s="29"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
-      <c r="M54" s="28"/>
-      <c r="N54" s="28"/>
-      <c r="O54" s="28"/>
-      <c r="P54" s="28"/>
-      <c r="Q54" s="28"/>
-      <c r="R54" s="28"/>
-      <c r="S54" s="45"/>
-      <c r="T54" s="28"/>
-      <c r="U54" s="28"/>
-      <c r="V54" s="28"/>
-      <c r="W54" s="28"/>
-      <c r="X54" s="51" t="s">
+      <c r="F54" s="27"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="26"/>
+      <c r="O54" s="26"/>
+      <c r="P54" s="40"/>
+      <c r="Q54" s="26"/>
+      <c r="R54" s="26"/>
+      <c r="S54" s="47"/>
+      <c r="T54" s="26"/>
+      <c r="U54" s="26"/>
+      <c r="V54" s="26"/>
+      <c r="W54" s="26"/>
+      <c r="X54" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y54" s="58"/>
-      <c r="Z54" s="58"/>
-      <c r="AA54" s="58"/>
-      <c r="AB54" s="58"/>
+      <c r="Y54" s="59"/>
+      <c r="Z54" s="59"/>
+      <c r="AA54" s="59"/>
+      <c r="AB54" s="59"/>
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:28">
       <c r="A55" s="9"/>
@@ -5205,35 +5220,35 @@
       <c r="D55" s="11">
         <v>5</v>
       </c>
-      <c r="E55" s="27">
+      <c r="E55" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F55" s="29"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="28"/>
-      <c r="S55" s="45"/>
-      <c r="T55" s="28"/>
-      <c r="U55" s="28"/>
-      <c r="V55" s="28"/>
-      <c r="W55" s="28"/>
-      <c r="X55" s="51" t="s">
+      <c r="F55" s="27"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="26"/>
+      <c r="O55" s="26"/>
+      <c r="P55" s="40"/>
+      <c r="Q55" s="26"/>
+      <c r="R55" s="26"/>
+      <c r="S55" s="47"/>
+      <c r="T55" s="26"/>
+      <c r="U55" s="26"/>
+      <c r="V55" s="26"/>
+      <c r="W55" s="26"/>
+      <c r="X55" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y55" s="58"/>
-      <c r="Z55" s="58"/>
-      <c r="AA55" s="58"/>
-      <c r="AB55" s="58"/>
+      <c r="Y55" s="59"/>
+      <c r="Z55" s="59"/>
+      <c r="AA55" s="59"/>
+      <c r="AB55" s="59"/>
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:28">
       <c r="A56" s="9"/>
@@ -5242,35 +5257,37 @@
         <v>77</v>
       </c>
       <c r="D56" s="11">
-        <v>3</v>
-      </c>
-      <c r="E56" s="27">
+        <v>5</v>
+      </c>
+      <c r="E56" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F56" s="29"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
-      <c r="J56" s="28"/>
-      <c r="K56" s="28"/>
-      <c r="L56" s="28"/>
-      <c r="M56" s="28"/>
-      <c r="N56" s="28"/>
-      <c r="O56" s="28"/>
-      <c r="P56" s="28"/>
-      <c r="Q56" s="28"/>
-      <c r="R56" s="28"/>
-      <c r="S56" s="45"/>
-      <c r="T56" s="28"/>
-      <c r="U56" s="28"/>
-      <c r="V56" s="28"/>
-      <c r="W56" s="28"/>
-      <c r="X56" s="51"/>
-      <c r="Y56" s="58"/>
-      <c r="Z56" s="58"/>
-      <c r="AA56" s="58"/>
-      <c r="AB56" s="58"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="26"/>
+      <c r="O56" s="26"/>
+      <c r="P56" s="26"/>
+      <c r="Q56" s="40"/>
+      <c r="R56" s="26"/>
+      <c r="S56" s="47"/>
+      <c r="T56" s="26"/>
+      <c r="U56" s="26"/>
+      <c r="V56" s="26"/>
+      <c r="W56" s="26"/>
+      <c r="X56" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y56" s="59"/>
+      <c r="Z56" s="59"/>
+      <c r="AA56" s="59"/>
+      <c r="AB56" s="59"/>
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:28">
       <c r="A57" s="9"/>
@@ -5281,35 +5298,33 @@
       <c r="D57" s="11">
         <v>3</v>
       </c>
-      <c r="E57" s="27">
+      <c r="E57" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F57" s="29"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
-      <c r="N57" s="28"/>
-      <c r="O57" s="28"/>
-      <c r="P57" s="28"/>
-      <c r="Q57" s="28"/>
-      <c r="R57" s="28"/>
-      <c r="S57" s="45"/>
-      <c r="T57" s="28"/>
-      <c r="U57" s="28"/>
-      <c r="V57" s="28"/>
-      <c r="W57" s="28"/>
-      <c r="X57" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y57" s="58"/>
-      <c r="Z57" s="58"/>
-      <c r="AA57" s="58"/>
-      <c r="AB57" s="58"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="26"/>
+      <c r="Q57" s="40"/>
+      <c r="R57" s="26"/>
+      <c r="S57" s="47"/>
+      <c r="T57" s="26"/>
+      <c r="U57" s="26"/>
+      <c r="V57" s="26"/>
+      <c r="W57" s="26"/>
+      <c r="X57" s="53"/>
+      <c r="Y57" s="59"/>
+      <c r="Z57" s="59"/>
+      <c r="AA57" s="59"/>
+      <c r="AB57" s="59"/>
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:28">
       <c r="A58" s="9"/>
@@ -5318,37 +5333,37 @@
         <v>79</v>
       </c>
       <c r="D58" s="11">
-        <v>6</v>
-      </c>
-      <c r="E58" s="27">
+        <v>3</v>
+      </c>
+      <c r="E58" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F58" s="29"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="28"/>
-      <c r="S58" s="45"/>
-      <c r="T58" s="28"/>
-      <c r="U58" s="28"/>
-      <c r="V58" s="28"/>
-      <c r="W58" s="28"/>
-      <c r="X58" s="51" t="s">
+      <c r="F58" s="27"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="26"/>
+      <c r="O58" s="26"/>
+      <c r="P58" s="26"/>
+      <c r="Q58" s="26"/>
+      <c r="R58" s="40"/>
+      <c r="S58" s="47"/>
+      <c r="T58" s="26"/>
+      <c r="U58" s="26"/>
+      <c r="V58" s="26"/>
+      <c r="W58" s="26"/>
+      <c r="X58" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y58" s="58"/>
-      <c r="Z58" s="58"/>
-      <c r="AA58" s="58"/>
-      <c r="AB58" s="58"/>
+      <c r="Y58" s="59"/>
+      <c r="Z58" s="59"/>
+      <c r="AA58" s="59"/>
+      <c r="AB58" s="59"/>
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:28">
       <c r="A59" s="9"/>
@@ -5357,37 +5372,37 @@
         <v>80</v>
       </c>
       <c r="D59" s="11">
-        <v>5</v>
-      </c>
-      <c r="E59" s="27">
+        <v>6</v>
+      </c>
+      <c r="E59" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F59" s="29"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="28"/>
-      <c r="M59" s="28"/>
-      <c r="N59" s="28"/>
-      <c r="O59" s="28"/>
-      <c r="P59" s="28"/>
-      <c r="Q59" s="28"/>
-      <c r="R59" s="28"/>
-      <c r="S59" s="45"/>
-      <c r="T59" s="28"/>
-      <c r="U59" s="28"/>
-      <c r="V59" s="28"/>
-      <c r="W59" s="28"/>
-      <c r="X59" s="51" t="s">
+      <c r="F59" s="27"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="26"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="26"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="26"/>
+      <c r="O59" s="26"/>
+      <c r="P59" s="26"/>
+      <c r="Q59" s="26"/>
+      <c r="R59" s="40"/>
+      <c r="S59" s="47"/>
+      <c r="T59" s="26"/>
+      <c r="U59" s="26"/>
+      <c r="V59" s="26"/>
+      <c r="W59" s="26"/>
+      <c r="X59" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y59" s="58"/>
-      <c r="Z59" s="58"/>
-      <c r="AA59" s="58"/>
-      <c r="AB59" s="58"/>
+      <c r="Y59" s="59"/>
+      <c r="Z59" s="59"/>
+      <c r="AA59" s="59"/>
+      <c r="AB59" s="59"/>
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:28">
       <c r="A60" s="9"/>
@@ -5396,174 +5411,170 @@
         <v>81</v>
       </c>
       <c r="D60" s="11">
-        <v>3</v>
-      </c>
-      <c r="E60" s="27">
+        <v>5</v>
+      </c>
+      <c r="E60" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F60" s="29"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="28"/>
-      <c r="M60" s="28"/>
-      <c r="N60" s="28"/>
-      <c r="O60" s="28"/>
-      <c r="P60" s="28"/>
-      <c r="Q60" s="28"/>
-      <c r="R60" s="28"/>
-      <c r="S60" s="45"/>
-      <c r="T60" s="28"/>
-      <c r="U60" s="28"/>
-      <c r="V60" s="28"/>
-      <c r="W60" s="28"/>
-      <c r="X60" s="51" t="s">
+      <c r="F60" s="27"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="26"/>
+      <c r="O60" s="26"/>
+      <c r="P60" s="26"/>
+      <c r="Q60" s="26"/>
+      <c r="R60" s="26"/>
+      <c r="S60" s="47"/>
+      <c r="T60" s="40"/>
+      <c r="U60" s="26"/>
+      <c r="V60" s="26"/>
+      <c r="W60" s="26"/>
+      <c r="X60" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y60" s="58"/>
-      <c r="Z60" s="58"/>
-      <c r="AA60" s="58"/>
-      <c r="AB60" s="58"/>
+      <c r="Y60" s="59"/>
+      <c r="Z60" s="59"/>
+      <c r="AA60" s="59"/>
+      <c r="AB60" s="59"/>
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:28">
       <c r="A61" s="9"/>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="12"/>
+      <c r="C61" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="10"/>
       <c r="D61" s="11">
-        <f>SUM(D62:D63)</f>
-        <v>20</v>
-      </c>
-      <c r="E61" s="27">
+        <v>3</v>
+      </c>
+      <c r="E61" s="25">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="F61" s="33">
-        <f t="shared" ref="F61:W61" si="17">SUM(F62:F63)</f>
-        <v>0</v>
-      </c>
-      <c r="G61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="I61" s="36">
-        <f t="shared" si="17"/>
-        <v>4</v>
-      </c>
-      <c r="J61" s="36">
-        <f t="shared" si="17"/>
-        <v>4</v>
-      </c>
-      <c r="K61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="L61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="N61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="O61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P61" s="28">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R61" s="28">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="S61" s="45">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="T61" s="28">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="U61" s="28">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V61" s="28">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="W61" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="X61" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="F61" s="27"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
+      <c r="R61" s="26"/>
+      <c r="S61" s="47"/>
+      <c r="T61" s="40"/>
+      <c r="U61" s="26"/>
+      <c r="V61" s="26"/>
+      <c r="W61" s="26"/>
+      <c r="X61" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y61" s="58"/>
-      <c r="Z61" s="58"/>
-      <c r="AA61" s="58"/>
-      <c r="AB61" s="58"/>
+      <c r="Y61" s="59"/>
+      <c r="Z61" s="59"/>
+      <c r="AA61" s="59"/>
+      <c r="AB61" s="59"/>
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:28">
       <c r="A62" s="9"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="13" t="s">
+      <c r="B62" s="10" t="s">
         <v>83</v>
       </c>
+      <c r="C62" s="10"/>
       <c r="D62" s="11">
-        <v>5</v>
-      </c>
-      <c r="E62" s="27">
+        <f>SUM(D63:D64)</f>
+        <v>20</v>
+      </c>
+      <c r="E62" s="25">
         <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="F62" s="31">
+        <f t="shared" ref="F62:W62" si="17">SUM(F63:F64)</f>
+        <v>0</v>
+      </c>
+      <c r="G62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="34">
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="F62" s="29"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="28">
-        <v>2</v>
-      </c>
-      <c r="J62" s="28">
-        <v>2</v>
-      </c>
-      <c r="K62" s="28"/>
-      <c r="L62" s="28"/>
-      <c r="M62" s="28"/>
-      <c r="N62" s="28"/>
-      <c r="O62" s="28"/>
-      <c r="P62" s="28"/>
-      <c r="Q62" s="28"/>
-      <c r="R62" s="28"/>
-      <c r="S62" s="45"/>
-      <c r="T62" s="28"/>
-      <c r="U62" s="28"/>
-      <c r="V62" s="28"/>
-      <c r="W62" s="28"/>
-      <c r="X62" s="51" t="s">
+      <c r="J62" s="34">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="K62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="N62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P62" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R62" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="S62" s="47">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="T62" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U62" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V62" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="W62" s="34">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X62" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y62" s="58"/>
-      <c r="Z62" s="58"/>
-      <c r="AA62" s="58"/>
-      <c r="AB62" s="58"/>
+      <c r="Y62" s="59"/>
+      <c r="Z62" s="59"/>
+      <c r="AA62" s="59"/>
+      <c r="AB62" s="59"/>
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:28">
       <c r="A63" s="9"/>
@@ -5572,284 +5583,326 @@
         <v>84</v>
       </c>
       <c r="D63" s="11">
-        <v>15</v>
-      </c>
-      <c r="E63" s="27">
+        <v>5</v>
+      </c>
+      <c r="E63" s="25">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F63" s="29"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="28">
+      <c r="F63" s="27"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26">
         <v>2</v>
       </c>
-      <c r="J63" s="28">
+      <c r="J63" s="26">
         <v>2</v>
       </c>
-      <c r="K63" s="28"/>
-      <c r="L63" s="28"/>
-      <c r="M63" s="28"/>
-      <c r="N63" s="28"/>
-      <c r="O63" s="28"/>
-      <c r="P63" s="28"/>
-      <c r="Q63" s="28"/>
-      <c r="R63" s="28"/>
-      <c r="S63" s="45"/>
-      <c r="T63" s="28"/>
-      <c r="U63" s="28"/>
-      <c r="V63" s="28"/>
-      <c r="W63" s="28"/>
-      <c r="X63" s="51" t="s">
+      <c r="K63" s="26"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="26"/>
+      <c r="Q63" s="26"/>
+      <c r="R63" s="26"/>
+      <c r="S63" s="47"/>
+      <c r="T63" s="26"/>
+      <c r="U63" s="26"/>
+      <c r="V63" s="26"/>
+      <c r="W63" s="26"/>
+      <c r="X63" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y63" s="58"/>
-      <c r="Z63" s="58"/>
-      <c r="AA63" s="58"/>
-      <c r="AB63" s="58"/>
+      <c r="Y63" s="59"/>
+      <c r="Z63" s="59"/>
+      <c r="AA63" s="59"/>
+      <c r="AB63" s="59"/>
     </row>
-    <row r="64" ht="18.75" customHeight="1" spans="2:28">
-      <c r="B64" s="19" t="s">
+    <row r="64" ht="18.75" customHeight="1" spans="1:28">
+      <c r="A64" s="9"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="19"/>
-      <c r="D64" s="20">
-        <f t="shared" ref="D64:V64" si="18">D29+D17+D3</f>
-        <v>273</v>
-      </c>
-      <c r="E64" s="20">
+      <c r="D64" s="11">
+        <v>15</v>
+      </c>
+      <c r="E64" s="25">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F64" s="27"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26">
+        <v>2</v>
+      </c>
+      <c r="J64" s="26">
+        <v>2</v>
+      </c>
+      <c r="K64" s="26"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="26"/>
+      <c r="O64" s="26"/>
+      <c r="P64" s="26"/>
+      <c r="Q64" s="26"/>
+      <c r="R64" s="26"/>
+      <c r="S64" s="47"/>
+      <c r="T64" s="26"/>
+      <c r="U64" s="26"/>
+      <c r="V64" s="26"/>
+      <c r="W64" s="26"/>
+      <c r="X64" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y64" s="59"/>
+      <c r="Z64" s="59"/>
+      <c r="AA64" s="59"/>
+      <c r="AB64" s="59"/>
+    </row>
+    <row r="65" ht="18.75" customHeight="1" spans="2:28">
+      <c r="B65" s="82" t="s">
+        <v>86</v>
+      </c>
+      <c r="C65" s="82"/>
+      <c r="D65" s="83">
+        <f t="shared" ref="D65:V65" si="18">D29+D17+D3</f>
+        <v>278</v>
+      </c>
+      <c r="E65" s="83">
         <f t="shared" si="18"/>
-        <v>75</v>
-      </c>
-      <c r="F64" s="20">
+        <v>77</v>
+      </c>
+      <c r="F65" s="83">
         <f t="shared" si="18"/>
         <v>15</v>
       </c>
-      <c r="G64" s="20">
+      <c r="G65" s="83">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="H64" s="20">
+      <c r="H65" s="83">
         <f t="shared" si="18"/>
         <v>15</v>
       </c>
-      <c r="I64" s="20">
+      <c r="I65" s="83">
         <f t="shared" si="18"/>
         <v>16</v>
       </c>
-      <c r="J64" s="20">
+      <c r="J65" s="83">
         <f t="shared" si="18"/>
         <v>17</v>
       </c>
-      <c r="K64" s="20">
+      <c r="K65" s="83">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="L64" s="20">
+        <v>2</v>
+      </c>
+      <c r="L65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="M64" s="20">
+      <c r="M65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="N64" s="20">
+      <c r="N65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O64" s="20">
+      <c r="O65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="P64" s="20">
+      <c r="P65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q64" s="20">
+      <c r="Q65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="R64" s="20">
+      <c r="R65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="S64" s="20">
+      <c r="S65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="T64" s="20">
+      <c r="T65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U64" s="20">
+      <c r="U65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="V64" s="20">
+      <c r="V65" s="83">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="W64" s="20"/>
-      <c r="X64" s="57"/>
-      <c r="Y64" s="58"/>
-      <c r="Z64" s="58"/>
-      <c r="AA64" s="58"/>
-      <c r="AB64" s="58"/>
-    </row>
-    <row r="65" ht="18.75" customHeight="1" spans="3:28">
-      <c r="C65" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D65" s="81">
-        <f>SUM(F65:V65)</f>
-        <v>240</v>
-      </c>
-      <c r="E65" s="81">
-        <f>SUM(F65:V65)</f>
-        <v>240</v>
-      </c>
-      <c r="F65" s="82">
-        <v>15</v>
-      </c>
-      <c r="G65" s="82">
-        <v>15</v>
-      </c>
-      <c r="H65" s="82">
-        <v>15</v>
-      </c>
-      <c r="I65" s="82">
-        <v>15</v>
-      </c>
-      <c r="J65" s="82">
-        <v>15</v>
-      </c>
-      <c r="K65" s="82">
-        <v>15</v>
-      </c>
-      <c r="L65" s="82">
-        <v>15</v>
-      </c>
-      <c r="M65" s="82">
-        <v>15</v>
-      </c>
-      <c r="N65" s="82">
-        <v>15</v>
-      </c>
-      <c r="O65" s="82">
-        <v>15</v>
-      </c>
-      <c r="P65" s="82">
-        <v>15</v>
-      </c>
-      <c r="Q65" s="82">
-        <v>15</v>
-      </c>
-      <c r="R65" s="82">
-        <v>15</v>
-      </c>
-      <c r="S65" s="82">
-        <v>0</v>
-      </c>
-      <c r="T65" s="82">
-        <v>15</v>
-      </c>
-      <c r="U65" s="82">
-        <v>15</v>
-      </c>
-      <c r="V65" s="82">
-        <v>15</v>
-      </c>
-      <c r="Y65" s="58"/>
-      <c r="Z65" s="58"/>
-      <c r="AA65" s="58"/>
-      <c r="AB65" s="58"/>
+      <c r="W65" s="83"/>
+      <c r="X65" s="86"/>
+      <c r="Y65" s="59"/>
+      <c r="Z65" s="59"/>
+      <c r="AA65" s="59"/>
+      <c r="AB65" s="59"/>
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="3:28">
       <c r="C66" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D66" s="81">
-        <f t="shared" ref="D66:V66" si="19">D65-D64</f>
-        <v>-33</v>
-      </c>
-      <c r="E66" s="81">
+      <c r="D66" s="84">
+        <f>SUM(F66:V66)</f>
+        <v>240</v>
+      </c>
+      <c r="E66" s="84">
+        <f>SUM(F66:V66)</f>
+        <v>240</v>
+      </c>
+      <c r="F66" s="85">
+        <v>15</v>
+      </c>
+      <c r="G66" s="85">
+        <v>15</v>
+      </c>
+      <c r="H66" s="85">
+        <v>15</v>
+      </c>
+      <c r="I66" s="85">
+        <v>15</v>
+      </c>
+      <c r="J66" s="85">
+        <v>15</v>
+      </c>
+      <c r="K66" s="85">
+        <v>15</v>
+      </c>
+      <c r="L66" s="85">
+        <v>15</v>
+      </c>
+      <c r="M66" s="85">
+        <v>15</v>
+      </c>
+      <c r="N66" s="85">
+        <v>15</v>
+      </c>
+      <c r="O66" s="85">
+        <v>15</v>
+      </c>
+      <c r="P66" s="85">
+        <v>15</v>
+      </c>
+      <c r="Q66" s="85">
+        <v>15</v>
+      </c>
+      <c r="R66" s="85">
+        <v>15</v>
+      </c>
+      <c r="S66" s="85">
+        <v>0</v>
+      </c>
+      <c r="T66" s="85">
+        <v>15</v>
+      </c>
+      <c r="U66" s="85">
+        <v>15</v>
+      </c>
+      <c r="V66" s="85">
+        <v>15</v>
+      </c>
+      <c r="Y66" s="59"/>
+      <c r="Z66" s="59"/>
+      <c r="AA66" s="59"/>
+      <c r="AB66" s="59"/>
+    </row>
+    <row r="67" ht="18.75" customHeight="1" spans="3:28">
+      <c r="C67" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="84">
+        <f t="shared" ref="D67:V67" si="19">D66-D65</f>
+        <v>-38</v>
+      </c>
+      <c r="E67" s="84">
         <f t="shared" si="19"/>
-        <v>165</v>
-      </c>
-      <c r="F66" s="81">
+        <v>163</v>
+      </c>
+      <c r="F67" s="84">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="G66" s="81">
+      <c r="G67" s="84">
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="H66" s="81">
+      <c r="H67" s="84">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I66" s="81">
+      <c r="I67" s="84">
         <f t="shared" si="19"/>
         <v>-1</v>
       </c>
-      <c r="J66" s="81">
+      <c r="J67" s="84">
         <f t="shared" si="19"/>
         <v>-2</v>
       </c>
-      <c r="K66" s="81">
+      <c r="K67" s="84">
+        <f t="shared" si="19"/>
+        <v>13</v>
+      </c>
+      <c r="L67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="L66" s="81">
+      <c r="M67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="M66" s="81">
+      <c r="N67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="N66" s="81">
+      <c r="O67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="O66" s="81">
+      <c r="P67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="P66" s="81">
+      <c r="Q67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="Q66" s="81">
+      <c r="R67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="R66" s="81">
+      <c r="S67" s="84">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="T67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="S66" s="81">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T66" s="81">
+      <c r="U67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="U66" s="81">
+      <c r="V67" s="84">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="V66" s="81">
-        <f t="shared" si="19"/>
-        <v>15</v>
-      </c>
-      <c r="Y66" s="83"/>
-      <c r="Z66" s="84"/>
-      <c r="AA66" s="83"/>
-      <c r="AB66" s="83"/>
+      <c r="Y67" s="87"/>
+      <c r="Z67" s="88"/>
+      <c r="AA67" s="87"/>
+      <c r="AB67" s="87"/>
     </row>
-    <row r="67" ht="18.75" customHeight="1"/>
     <row r="68" ht="18.75" customHeight="1"/>
     <row r="69" ht="18.75" customHeight="1"/>
     <row r="70" ht="18.75" customHeight="1"/>
@@ -6035,7 +6088,7 @@
     <row r="250" ht="18.75" customHeight="1"/>
     <row r="251" ht="18.75" customHeight="1"/>
     <row r="252" ht="18.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="253" ht="18.75" customHeight="1"/>
     <row r="254" ht="15.75" customHeight="1"/>
     <row r="255" ht="15.75" customHeight="1"/>
     <row r="256" ht="15.75" customHeight="1"/>
@@ -6782,6 +6835,7 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="A1:C1"/>
@@ -6804,8 +6858,8 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B65:C65"/>
     <mergeCell ref="Z19:AA20"/>
     <mergeCell ref="Z21:AA22"/>
   </mergeCells>
@@ -6921,7 +6975,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58">
+  <conditionalFormatting sqref="E59">
     <cfRule type="expression" dxfId="0" priority="114">
       <formula>#REF!&lt;#REF!</formula>
     </cfRule>
@@ -6935,12 +6989,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D64:W64">
+  <conditionalFormatting sqref="D65:W65">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D66:V66">
+  <conditionalFormatting sqref="D67:V67">
     <cfRule type="cellIs" dxfId="6" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -7108,7 +7162,7 @@
       <formula>"Very Late &amp; Complete"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X52:X63">
+  <conditionalFormatting sqref="X52:X64">
     <cfRule type="cellIs" dxfId="8" priority="61" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
@@ -7139,7 +7193,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V4:W4 F7:W7 F18:W18 F21:W21 F30:W30 F47:W47 D64:W64 F40:W40">
+  <conditionalFormatting sqref="V4:W4 F7:W7 F18:W18 F21:W21 F30:W30 F47:W47 D65:W65 F40:W40">
     <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -7209,12 +7263,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D52 D61">
+  <conditionalFormatting sqref="D52 D62">
     <cfRule type="cellIs" dxfId="3" priority="76" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E57 E61:E62">
+  <conditionalFormatting sqref="E62:E63 E52:E58">
     <cfRule type="expression" dxfId="0" priority="118">
       <formula>E42&lt;D42</formula>
     </cfRule>
@@ -7228,22 +7282,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F52:W52 F61:W61">
+  <conditionalFormatting sqref="F52:W52 F62:W62">
     <cfRule type="cellIs" dxfId="4" priority="60" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P52 P61">
+  <conditionalFormatting sqref="P52 P62">
     <cfRule type="cellIs" dxfId="4" priority="106" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S52 S61">
+  <conditionalFormatting sqref="S52 S62">
     <cfRule type="cellIs" dxfId="4" priority="112" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E59:E60 E63">
+  <conditionalFormatting sqref="E60:E61 E64">
     <cfRule type="expression" dxfId="0" priority="56">
       <formula>E48&lt;D48</formula>
     </cfRule>
@@ -7258,7 +7312,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="X16 X28 X4:X7 X10:X11 X13:X14 X18:X23 X25:X26 X30:X63">
+    <dataValidation type="list" allowBlank="1" sqref="X16 X28 X4:X7 X10:X11 X13:X14 X18:X23 X25:X26 X30:X64">
       <formula1>"Complete,Early &amp; Complete,Ontime (In Progress),Late (In Progress),Very Late &amp; Complete,Very Late (In Progress),Not Started,Late &amp; Complete"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="X12 X15 X24 X27 X8:X9">

--- a/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
+++ b/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12210" tabRatio="500"/>
+    <workbookView windowWidth="28800" windowHeight="12300" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="89">
   <si>
     <t>Total Hours</t>
   </si>
@@ -304,22 +304,22 @@
     <t>MCT: Review test docs</t>
   </si>
   <si>
+    <t>MCT: Bench setup</t>
+  </si>
+  <si>
+    <t>Learning Hydra</t>
+  </si>
+  <si>
+    <t>MCT: Hydra development</t>
+  </si>
+  <si>
+    <t>MCT: Hydra hardwired to Li2</t>
+  </si>
+  <si>
+    <t>MCT: Hydra hardwired to CDH to Li2</t>
+  </si>
+  <si>
     <t>Late (In Progress)</t>
-  </si>
-  <si>
-    <t>MCT: Bench setup</t>
-  </si>
-  <si>
-    <t>Learning Hydra</t>
-  </si>
-  <si>
-    <t>MCT: Hydra development</t>
-  </si>
-  <si>
-    <t>MCT: Hydra hardwired to Li2</t>
-  </si>
-  <si>
-    <t>MCT: Hydra hardwired to CDH to Li2</t>
   </si>
   <si>
     <t>MCT: Practice run-through of test</t>
@@ -422,11 +422,11 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="m\/d"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -523,13 +523,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -538,8 +531,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -552,10 +560,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -591,14 +600,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -623,7 +624,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -636,17 +637,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -657,18 +664,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="48">
@@ -770,7 +765,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -782,49 +891,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,121 +945,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1332,16 +1327,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1356,16 +1351,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1388,134 +1383,134 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="44" borderId="36" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="44" borderId="36" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2307,7 +2302,7 @@
       </c>
       <c r="E3" s="23">
         <f t="shared" ref="E3:E64" si="1">SUM(F3:W3)</f>
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F3" s="24">
         <f t="shared" ref="F3:V3" si="2">F4+F7+F11+F14</f>
@@ -2331,7 +2326,7 @@
       </c>
       <c r="K3" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" s="24">
         <f t="shared" si="2"/>
@@ -2400,7 +2395,7 @@
       </c>
       <c r="E4" s="25">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F4" s="26">
         <f t="shared" ref="F4:W4" si="3">SUM(F5:F6)</f>
@@ -2424,7 +2419,7 @@
       </c>
       <c r="K4" s="26">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="26">
         <f t="shared" si="3"/>
@@ -2499,7 +2494,7 @@
       </c>
       <c r="E5" s="25">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="27">
         <v>1</v>
@@ -2516,7 +2511,9 @@
       <c r="J5" s="26">
         <v>1</v>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="26">
+        <v>1</v>
+      </c>
       <c r="L5" s="26"/>
       <c r="M5" s="26"/>
       <c r="N5" s="26"/>
@@ -2554,7 +2551,7 @@
       </c>
       <c r="E6" s="28">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="29">
         <v>2</v>
@@ -2571,7 +2568,9 @@
       <c r="J6" s="30">
         <v>2</v>
       </c>
-      <c r="K6" s="30"/>
+      <c r="K6" s="30">
+        <v>2</v>
+      </c>
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
@@ -2608,7 +2607,7 @@
       </c>
       <c r="E7" s="25">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F7" s="31">
         <f t="shared" ref="F7:W7" si="4">SUM(F8:F10)</f>
@@ -2632,7 +2631,7 @@
       </c>
       <c r="K7" s="31">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="31">
         <f t="shared" si="4"/>
@@ -2705,7 +2704,7 @@
       </c>
       <c r="E8" s="25">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="27">
         <v>1</v>
@@ -2722,7 +2721,9 @@
       <c r="J8" s="26">
         <v>1</v>
       </c>
-      <c r="K8" s="26"/>
+      <c r="K8" s="26">
+        <v>1</v>
+      </c>
       <c r="L8" s="26"/>
       <c r="M8" s="26"/>
       <c r="N8" s="26"/>
@@ -2758,7 +2759,7 @@
       </c>
       <c r="E9" s="25">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="27">
         <v>1</v>
@@ -2775,7 +2776,9 @@
       <c r="J9" s="26">
         <v>1</v>
       </c>
-      <c r="K9" s="26"/>
+      <c r="K9" s="26">
+        <v>1</v>
+      </c>
       <c r="L9" s="26"/>
       <c r="M9" s="26"/>
       <c r="N9" s="26"/>
@@ -2807,7 +2810,7 @@
       </c>
       <c r="E10" s="28">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" s="29">
         <v>2</v>
@@ -2824,7 +2827,9 @@
       <c r="J10" s="30">
         <v>3</v>
       </c>
-      <c r="K10" s="30"/>
+      <c r="K10" s="30">
+        <v>2</v>
+      </c>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
@@ -3238,7 +3243,7 @@
       </c>
       <c r="E17" s="23">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="32">
         <f t="shared" ref="F17:V17" si="7">F18+F21+F23+F26</f>
@@ -3262,7 +3267,7 @@
       </c>
       <c r="K17" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="32">
         <f t="shared" si="7"/>
@@ -3509,7 +3514,7 @@
       </c>
       <c r="E21" s="25">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" s="31">
         <f t="shared" ref="F21:W21" si="9">SUM(F22)</f>
@@ -3533,7 +3538,7 @@
       </c>
       <c r="K21" s="31">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="31">
         <f t="shared" si="9"/>
@@ -3604,7 +3609,7 @@
       </c>
       <c r="E22" s="25">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="27"/>
       <c r="G22" s="26"/>
@@ -3617,7 +3622,9 @@
       <c r="J22" s="26">
         <v>1</v>
       </c>
-      <c r="K22" s="26"/>
+      <c r="K22" s="26">
+        <v>1</v>
+      </c>
       <c r="L22" s="26"/>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
@@ -3931,7 +3938,7 @@
       </c>
       <c r="E29" s="23">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F29" s="32">
         <f t="shared" ref="F29:V29" si="12">F30+F40+F47+F52+F62</f>
@@ -3955,7 +3962,7 @@
       </c>
       <c r="K29" s="32">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L29" s="32">
         <f t="shared" si="12"/>
@@ -4020,7 +4027,7 @@
       </c>
       <c r="E30" s="25">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F30" s="31">
         <f t="shared" ref="F30:W30" si="13">SUM(F31:F39)</f>
@@ -4044,7 +4051,7 @@
       </c>
       <c r="K30" s="34">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L30" s="34">
         <f t="shared" si="13"/>
@@ -4140,7 +4147,7 @@
       <c r="V31" s="26"/>
       <c r="W31" s="26"/>
       <c r="X31" s="58" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="Y31" s="59"/>
       <c r="Z31" s="59"/>
@@ -4151,7 +4158,7 @@
       <c r="A32" s="9"/>
       <c r="B32" s="12"/>
       <c r="C32" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="11">
         <v>2</v>
@@ -4183,7 +4190,7 @@
       <c r="V32" s="26"/>
       <c r="W32" s="26"/>
       <c r="X32" s="58" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="Y32" s="59"/>
       <c r="Z32" s="59"/>
@@ -4194,7 +4201,7 @@
       <c r="A33" s="9"/>
       <c r="B33" s="12"/>
       <c r="C33" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33" s="11">
         <v>4</v>
@@ -4223,7 +4230,9 @@
       <c r="U33" s="26"/>
       <c r="V33" s="26"/>
       <c r="W33" s="26"/>
-      <c r="X33" s="58"/>
+      <c r="X33" s="58" t="s">
+        <v>16</v>
+      </c>
       <c r="Y33" s="59"/>
       <c r="Z33" s="59"/>
       <c r="AA33" s="59"/>
@@ -4233,21 +4242,23 @@
       <c r="A34" s="9"/>
       <c r="B34" s="12"/>
       <c r="C34" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D34" s="11">
         <v>4</v>
       </c>
       <c r="E34" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F34" s="27"/>
       <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="39"/>
       <c r="J34" s="26"/>
-      <c r="K34" s="40"/>
+      <c r="K34" s="40">
+        <v>4</v>
+      </c>
       <c r="L34" s="26"/>
       <c r="M34" s="26"/>
       <c r="N34" s="26"/>
@@ -4260,7 +4271,9 @@
       <c r="U34" s="26"/>
       <c r="V34" s="26"/>
       <c r="W34" s="26"/>
-      <c r="X34" s="58"/>
+      <c r="X34" s="58" t="s">
+        <v>16</v>
+      </c>
       <c r="Y34" s="59"/>
       <c r="Z34" s="59"/>
       <c r="AA34" s="59"/>
@@ -4270,21 +4283,23 @@
       <c r="A35" s="9"/>
       <c r="B35" s="12"/>
       <c r="C35" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D35" s="11">
         <v>4</v>
       </c>
       <c r="E35" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F35" s="27"/>
       <c r="G35" s="26"/>
       <c r="H35" s="26"/>
       <c r="I35" s="39"/>
       <c r="J35" s="26"/>
-      <c r="K35" s="40"/>
+      <c r="K35" s="40">
+        <v>4</v>
+      </c>
       <c r="L35" s="26"/>
       <c r="M35" s="26"/>
       <c r="N35" s="26"/>
@@ -4297,7 +4312,9 @@
       <c r="U35" s="26"/>
       <c r="V35" s="26"/>
       <c r="W35" s="26"/>
-      <c r="X35" s="58"/>
+      <c r="X35" s="58" t="s">
+        <v>16</v>
+      </c>
       <c r="Y35" s="59"/>
       <c r="Z35" s="59"/>
       <c r="AA35" s="59"/>
@@ -4307,21 +4324,23 @@
       <c r="A36" s="9"/>
       <c r="B36" s="12"/>
       <c r="C36" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" s="11">
         <v>4</v>
       </c>
       <c r="E36" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" s="27"/>
       <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="39"/>
       <c r="J36" s="26"/>
-      <c r="K36" s="40"/>
+      <c r="K36" s="40">
+        <v>2</v>
+      </c>
       <c r="L36" s="26"/>
       <c r="M36" s="26"/>
       <c r="N36" s="26"/>
@@ -4334,7 +4353,9 @@
       <c r="U36" s="26"/>
       <c r="V36" s="26"/>
       <c r="W36" s="26"/>
-      <c r="X36" s="58"/>
+      <c r="X36" s="58" t="s">
+        <v>57</v>
+      </c>
       <c r="Y36" s="59"/>
       <c r="Z36" s="59"/>
       <c r="AA36" s="59"/>
@@ -4351,14 +4372,16 @@
       </c>
       <c r="E37" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="27"/>
       <c r="G37" s="26"/>
       <c r="H37" s="26"/>
       <c r="I37" s="39"/>
       <c r="J37" s="26"/>
-      <c r="K37" s="40"/>
+      <c r="K37" s="40">
+        <v>1</v>
+      </c>
       <c r="L37" s="26"/>
       <c r="M37" s="26"/>
       <c r="N37" s="26"/>
@@ -4795,7 +4818,7 @@
       </c>
       <c r="E47" s="25">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F47" s="31">
         <f t="shared" ref="F47:W47" si="15">SUM(F48:F51)</f>
@@ -4819,7 +4842,7 @@
       </c>
       <c r="K47" s="34">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="34">
         <f t="shared" si="15"/>
@@ -5007,7 +5030,7 @@
       </c>
       <c r="E51" s="28">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F51" s="29"/>
       <c r="G51" s="30">
@@ -5018,7 +5041,9 @@
       </c>
       <c r="I51" s="30"/>
       <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
+      <c r="K51" s="30">
+        <v>2</v>
+      </c>
       <c r="L51" s="30"/>
       <c r="M51" s="30"/>
       <c r="N51" s="41"/>
@@ -5673,7 +5698,7 @@
       </c>
       <c r="E65" s="83">
         <f t="shared" si="18"/>
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="F65" s="83">
         <f t="shared" si="18"/>
@@ -5697,7 +5722,7 @@
       </c>
       <c r="K65" s="83">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L65" s="83">
         <f t="shared" si="18"/>
@@ -5828,7 +5853,7 @@
       </c>
       <c r="E67" s="84">
         <f t="shared" si="19"/>
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="F67" s="84">
         <f t="shared" si="19"/>
@@ -5852,7 +5877,7 @@
       </c>
       <c r="K67" s="84">
         <f t="shared" si="19"/>
-        <v>13</v>
+        <v>-8</v>
       </c>
       <c r="L67" s="84">
         <f t="shared" si="19"/>

--- a/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
+++ b/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300" tabRatio="500"/>
+    <workbookView windowWidth="28800" windowHeight="14100" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -319,10 +319,10 @@
     <t>MCT: Hydra hardwired to CDH to Li2</t>
   </si>
   <si>
-    <t>Late (In Progress)</t>
-  </si>
-  <si>
     <t>MCT: Practice run-through of test</t>
+  </si>
+  <si>
+    <t>Late &amp; Complete</t>
   </si>
   <si>
     <t>MCT: Full run through of test</t>
@@ -420,11 +420,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="m\/d"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -523,56 +523,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -592,8 +546,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -601,7 +570,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -615,10 +591,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -631,16 +607,46 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -652,17 +658,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -765,7 +765,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,127 +927,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -909,43 +945,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1287,7 +1287,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1296,7 +1296,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1312,17 +1312,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1352,6 +1341,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1366,151 +1370,147 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="47" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="44" borderId="36" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E3" s="23">
         <f t="shared" ref="E3:E64" si="1">SUM(F3:W3)</f>
-        <v>55</v>
+        <v>61.5</v>
       </c>
       <c r="F3" s="24">
         <f t="shared" ref="F3:V3" si="2">F4+F7+F11+F14</f>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="L3" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M3" s="24">
         <f t="shared" si="2"/>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E4" s="25">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4" s="26">
         <f t="shared" ref="F4:W4" si="3">SUM(F5:F6)</f>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="L4" s="26">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="26">
         <f t="shared" si="3"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="E5" s="25">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="27">
         <v>1</v>
@@ -2514,7 +2514,9 @@
       <c r="K5" s="26">
         <v>1</v>
       </c>
-      <c r="L5" s="26"/>
+      <c r="L5" s="26">
+        <v>1</v>
+      </c>
       <c r="M5" s="26"/>
       <c r="N5" s="26"/>
       <c r="O5" s="26"/>
@@ -2551,7 +2553,7 @@
       </c>
       <c r="E6" s="28">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" s="29">
         <v>2</v>
@@ -2571,7 +2573,9 @@
       <c r="K6" s="30">
         <v>2</v>
       </c>
-      <c r="L6" s="30"/>
+      <c r="L6" s="30">
+        <v>2</v>
+      </c>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
       <c r="O6" s="30"/>
@@ -2607,7 +2611,7 @@
       </c>
       <c r="E7" s="25">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>25.5</v>
       </c>
       <c r="F7" s="31">
         <f t="shared" ref="F7:W7" si="4">SUM(F8:F10)</f>
@@ -2635,7 +2639,7 @@
       </c>
       <c r="L7" s="31">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M7" s="31">
         <f t="shared" si="4"/>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="E8" s="25">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="27">
         <v>1</v>
@@ -2724,7 +2728,9 @@
       <c r="K8" s="26">
         <v>1</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="26">
+        <v>1</v>
+      </c>
       <c r="M8" s="26"/>
       <c r="N8" s="26"/>
       <c r="O8" s="26"/>
@@ -2759,7 +2765,7 @@
       </c>
       <c r="E9" s="25">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="27">
         <v>1</v>
@@ -2779,7 +2785,9 @@
       <c r="K9" s="26">
         <v>1</v>
       </c>
-      <c r="L9" s="26"/>
+      <c r="L9" s="26">
+        <v>1</v>
+      </c>
       <c r="M9" s="26"/>
       <c r="N9" s="26"/>
       <c r="O9" s="26"/>
@@ -2810,7 +2818,7 @@
       </c>
       <c r="E10" s="28">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="F10" s="29">
         <v>2</v>
@@ -2830,7 +2838,9 @@
       <c r="K10" s="30">
         <v>2</v>
       </c>
-      <c r="L10" s="30"/>
+      <c r="L10" s="30">
+        <v>1.5</v>
+      </c>
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
       <c r="O10" s="30"/>
@@ -3243,7 +3253,7 @@
       </c>
       <c r="E17" s="23">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" s="32">
         <f t="shared" ref="F17:V17" si="7">F18+F21+F23+F26</f>
@@ -3271,7 +3281,7 @@
       </c>
       <c r="L17" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="32">
         <f t="shared" si="7"/>
@@ -3514,7 +3524,7 @@
       </c>
       <c r="E21" s="25">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" s="31">
         <f t="shared" ref="F21:W21" si="9">SUM(F22)</f>
@@ -3542,7 +3552,7 @@
       </c>
       <c r="L21" s="31">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="31">
         <f t="shared" si="9"/>
@@ -3609,7 +3619,7 @@
       </c>
       <c r="E22" s="25">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" s="27"/>
       <c r="G22" s="26"/>
@@ -3625,7 +3635,9 @@
       <c r="K22" s="26">
         <v>1</v>
       </c>
-      <c r="L22" s="26"/>
+      <c r="L22" s="26">
+        <v>1</v>
+      </c>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
       <c r="O22" s="26"/>
@@ -3938,7 +3950,7 @@
       </c>
       <c r="E29" s="23">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F29" s="32">
         <f t="shared" ref="F29:V29" si="12">F30+F40+F47+F52+F62</f>
@@ -3966,7 +3978,7 @@
       </c>
       <c r="L29" s="32">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M29" s="32">
         <f t="shared" si="12"/>
@@ -4027,7 +4039,7 @@
       </c>
       <c r="E30" s="25">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F30" s="31">
         <f t="shared" ref="F30:W30" si="13">SUM(F31:F39)</f>
@@ -4055,7 +4067,7 @@
       </c>
       <c r="L30" s="34">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M30" s="34">
         <f t="shared" si="13"/>
@@ -4354,7 +4366,7 @@
       <c r="V36" s="26"/>
       <c r="W36" s="26"/>
       <c r="X36" s="58" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="Y36" s="59"/>
       <c r="Z36" s="59"/>
@@ -4365,14 +4377,14 @@
       <c r="A37" s="9"/>
       <c r="B37" s="12"/>
       <c r="C37" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" s="11">
         <v>2</v>
       </c>
       <c r="E37" s="25">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="27"/>
       <c r="G37" s="26"/>
@@ -4382,7 +4394,9 @@
       <c r="K37" s="40">
         <v>1</v>
       </c>
-      <c r="L37" s="26"/>
+      <c r="L37" s="26">
+        <v>1</v>
+      </c>
       <c r="M37" s="26"/>
       <c r="N37" s="26"/>
       <c r="O37" s="26"/>
@@ -4395,7 +4409,7 @@
       <c r="V37" s="26"/>
       <c r="W37" s="26"/>
       <c r="X37" s="58" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="Y37" s="59"/>
       <c r="Z37" s="59"/>
@@ -4413,7 +4427,7 @@
       </c>
       <c r="E38" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F38" s="27"/>
       <c r="G38" s="26"/>
@@ -4421,7 +4435,9 @@
       <c r="I38" s="39"/>
       <c r="J38" s="26"/>
       <c r="K38" s="26"/>
-      <c r="L38" s="40"/>
+      <c r="L38" s="40">
+        <v>3</v>
+      </c>
       <c r="M38" s="26"/>
       <c r="N38" s="26"/>
       <c r="O38" s="26"/>
@@ -4434,7 +4450,7 @@
       <c r="V38" s="26"/>
       <c r="W38" s="26"/>
       <c r="X38" s="58" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y38" s="59"/>
       <c r="Z38" s="59"/>
@@ -4452,7 +4468,7 @@
       </c>
       <c r="E39" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F39" s="27"/>
       <c r="G39" s="26"/>
@@ -4460,7 +4476,9 @@
       <c r="I39" s="39"/>
       <c r="J39" s="26"/>
       <c r="K39" s="26"/>
-      <c r="L39" s="40"/>
+      <c r="L39" s="40">
+        <v>2</v>
+      </c>
       <c r="M39" s="26"/>
       <c r="N39" s="26"/>
       <c r="O39" s="26"/>
@@ -4473,7 +4491,7 @@
       <c r="V39" s="26"/>
       <c r="W39" s="26"/>
       <c r="X39" s="58" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y39" s="59"/>
       <c r="Z39" s="59"/>
@@ -4492,7 +4510,7 @@
       </c>
       <c r="E40" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" s="31">
         <f t="shared" ref="F40:W40" si="14">SUM(F41:F46)</f>
@@ -4520,7 +4538,7 @@
       </c>
       <c r="L40" s="34">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="34">
         <f t="shared" si="14"/>
@@ -4585,7 +4603,7 @@
       </c>
       <c r="E41" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" s="27"/>
       <c r="G41" s="26"/>
@@ -4593,7 +4611,9 @@
       <c r="I41" s="39"/>
       <c r="J41" s="26"/>
       <c r="K41" s="26"/>
-      <c r="L41" s="40"/>
+      <c r="L41" s="40">
+        <v>2</v>
+      </c>
       <c r="M41" s="26"/>
       <c r="N41" s="26"/>
       <c r="O41" s="26"/>
@@ -5698,7 +5718,7 @@
       </c>
       <c r="E65" s="83">
         <f t="shared" si="18"/>
-        <v>98</v>
+        <v>113.5</v>
       </c>
       <c r="F65" s="83">
         <f t="shared" si="18"/>
@@ -5726,7 +5746,7 @@
       </c>
       <c r="L65" s="83">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="M65" s="83">
         <f t="shared" si="18"/>
@@ -5853,7 +5873,7 @@
       </c>
       <c r="E67" s="84">
         <f t="shared" si="19"/>
-        <v>142</v>
+        <v>126.5</v>
       </c>
       <c r="F67" s="84">
         <f t="shared" si="19"/>
@@ -5881,7 +5901,7 @@
       </c>
       <c r="L67" s="84">
         <f t="shared" si="19"/>
-        <v>15</v>
+        <v>-0.5</v>
       </c>
       <c r="M67" s="84">
         <f t="shared" si="19"/>

--- a/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
+++ b/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="96">
   <si>
     <t>Total Hours</t>
   </si>
@@ -413,6 +413,27 @@
   </si>
   <si>
     <t>Difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removed 10/14: Palo and Rainville own GS PC bring-up, my task is verifying it once it works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify GS PC in comms chain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocked until Palo/Rainville have the GS PC working, needs re-baseline (Palo approval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS PC bring-up owned by Palo and Rainville as of 10/14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ran 10/8 with Saanika, commands acknowledged through Hydra to CDH to Li-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Late (In Progress)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Started week of 10/5, finishing week of 10/12</t>
   </si>
 </sst>
 </file>
@@ -426,7 +447,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -664,6 +685,13 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Lato"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="48">
@@ -1518,7 +1546,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -1738,6 +1766,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4114,9 +4144,11 @@
         <v>0</v>
       </c>
       <c r="X30" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y30" s="59"/>
+        <v>58</v>
+      </c>
+      <c r="Y30" s="59" t="s">
+        <v>93</v>
+      </c>
       <c r="Z30" s="59"/>
       <c r="AA30" s="59"/>
       <c r="AB30" s="59"/>
@@ -4585,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="X40" s="53" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="Y40" s="59"/>
       <c r="Z40" s="59"/>
@@ -4626,9 +4658,11 @@
       <c r="V41" s="26"/>
       <c r="W41" s="26"/>
       <c r="X41" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y41" s="59"/>
+        <v>94</v>
+      </c>
+      <c r="Y41" s="59" t="s">
+        <v>95</v>
+      </c>
       <c r="Z41" s="59"/>
       <c r="AA41" s="59"/>
       <c r="AB41" s="59"/>
@@ -4915,7 +4949,9 @@
       <c r="X47" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y47" s="59"/>
+      <c r="Y47" s="59" t="s">
+        <v>92</v>
+      </c>
       <c r="Z47" s="59"/>
       <c r="AA47" s="59"/>
       <c r="AB47" s="59"/>
@@ -4923,7 +4959,7 @@
     <row r="48" ht="18.75" customHeight="1" spans="1:28">
       <c r="A48" s="9"/>
       <c r="B48" s="12"/>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="89" t="s">
         <v>69</v>
       </c>
       <c r="D48" s="11">
@@ -4956,7 +4992,9 @@
       <c r="X48" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Y48" s="59"/>
+      <c r="Y48" s="59" t="s">
+        <v>89</v>
+      </c>
       <c r="Z48" s="59"/>
       <c r="AA48" s="59"/>
       <c r="AB48" s="59"/>
@@ -4964,7 +5002,7 @@
     <row r="49" ht="18.75" customHeight="1" spans="1:28">
       <c r="A49" s="9"/>
       <c r="B49" s="12"/>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="89" t="s">
         <v>70</v>
       </c>
       <c r="D49" s="11">
@@ -4995,7 +5033,9 @@
       <c r="X49" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y49" s="59"/>
+      <c r="Y49" s="59" t="s">
+        <v>89</v>
+      </c>
       <c r="Z49" s="59"/>
       <c r="AA49" s="59"/>
       <c r="AB49" s="59"/>
@@ -5004,7 +5044,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="12"/>
       <c r="C50" s="13" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D50" s="11">
         <v>8</v>
@@ -5034,7 +5074,9 @@
       <c r="X50" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="Y50" s="59"/>
+      <c r="Y50" s="59" t="s">
+        <v>91</v>
+      </c>
       <c r="Z50" s="59"/>
       <c r="AA50" s="59"/>
       <c r="AB50" s="59"/>
@@ -5042,7 +5084,7 @@
     <row r="51" ht="18.75" customHeight="1" spans="1:28">
       <c r="A51" s="14"/>
       <c r="B51" s="15"/>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="90" t="s">
         <v>72</v>
       </c>
       <c r="D51" s="17">
@@ -5079,7 +5121,9 @@
       <c r="X51" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="Y51" s="59"/>
+      <c r="Y51" s="59" t="s">
+        <v>89</v>
+      </c>
       <c r="Z51" s="59"/>
       <c r="AA51" s="59"/>
       <c r="AB51" s="59"/>

--- a/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
+++ b/SWARM-EX/Planning/COMMS - Personal Waterfall Chart Justin Le.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14100" tabRatio="500"/>
+    <workbookView windowWidth="28800" windowHeight="12210" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -145,7 +145,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="90">
+  <si>
+    <t>Name: Justin Le</t>
+  </si>
   <si>
     <t>Total Hours</t>
   </si>
@@ -420,11 +423,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="m\/d"/>
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -434,21 +437,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Lato"/>
       <charset val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Lato"/>
       <charset val="1"/>
@@ -475,6 +472,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Lato"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
@@ -524,15 +527,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -540,6 +542,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -554,8 +571,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -570,66 +604,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -637,7 +611,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -658,6 +632,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -666,7 +669,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -699,7 +702,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor rgb="FF57BB8A"/>
       </patternFill>
     </fill>
@@ -717,14 +720,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA6A6A6"/>
         <bgColor rgb="FFB7B7B7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor rgb="FFFBBC04"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF3F3F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -765,7 +786,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,37 +876,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -819,7 +912,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -831,7 +936,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,109 +954,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1283,11 +1304,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1312,30 +1339,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1372,6 +1375,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1383,134 +1404,134 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="47" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="32" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1518,200 +1539,217 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="176" fontId="1" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="176" fontId="3" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1730,7 +1768,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -2164,3789 +2202,3791 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="19" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="59"/>
-      <c r="Z1" s="59"/>
-      <c r="AA1" s="59"/>
-      <c r="AB1" s="59"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="64"/>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="20">
+      <c r="E2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="22">
         <v>46258</v>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="23">
         <f t="shared" ref="G2:V2" si="0">F2+7</f>
         <v>46265</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="24">
         <f t="shared" si="0"/>
         <v>46272</v>
       </c>
-      <c r="I2" s="35">
+      <c r="I2" s="37">
         <f t="shared" si="0"/>
         <v>46279</v>
       </c>
-      <c r="J2" s="36">
+      <c r="J2" s="38">
         <f t="shared" si="0"/>
         <v>46286</v>
       </c>
-      <c r="K2" s="37">
+      <c r="K2" s="39">
         <f t="shared" si="0"/>
         <v>46293</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="38">
         <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-      <c r="M2" s="42">
+      <c r="M2" s="44">
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-      <c r="N2" s="36">
+      <c r="N2" s="45">
         <f t="shared" si="0"/>
         <v>46314</v>
       </c>
-      <c r="O2" s="36">
+      <c r="O2" s="45">
         <f t="shared" si="0"/>
         <v>46321</v>
       </c>
-      <c r="P2" s="37">
+      <c r="P2" s="46">
         <f t="shared" si="0"/>
         <v>46328</v>
       </c>
-      <c r="Q2" s="36">
+      <c r="Q2" s="45">
         <f t="shared" si="0"/>
         <v>46335</v>
       </c>
-      <c r="R2" s="37">
+      <c r="R2" s="46">
         <f t="shared" si="0"/>
         <v>46342</v>
       </c>
-      <c r="S2" s="42">
+      <c r="S2" s="51">
         <f t="shared" si="0"/>
         <v>46349</v>
       </c>
-      <c r="T2" s="37">
+      <c r="T2" s="46">
         <f t="shared" si="0"/>
         <v>46356</v>
       </c>
-      <c r="U2" s="42">
+      <c r="U2" s="51">
         <f t="shared" si="0"/>
         <v>46363</v>
       </c>
-      <c r="V2" s="42">
+      <c r="V2" s="51">
         <f t="shared" si="0"/>
         <v>46370</v>
       </c>
-      <c r="W2" s="37"/>
-      <c r="X2" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y2" s="60" t="s">
+      <c r="W2" s="46"/>
+      <c r="X2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="Z2" s="60" t="s">
+      <c r="Y2" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
+      <c r="Z2" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7">
+      <c r="A3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9">
         <f>D3/$D$65</f>
         <v>0.31294964028777</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="10">
         <f>D4+D7+D11+D14</f>
         <v>87</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="25">
         <f t="shared" ref="E3:E64" si="1">SUM(F3:W3)</f>
         <v>61.5</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="26">
         <f t="shared" ref="F3:V3" si="2">F4+F7+F11+F14</f>
         <v>14</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="26">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="26">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="26">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="26">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="26">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="26">
         <f t="shared" si="2"/>
         <v>6.5</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U3" s="24">
+      <c r="U3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V3" s="24">
+      <c r="V3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W3" s="51"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="59"/>
-      <c r="Z3" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA3" s="63" t="s">
+      <c r="W3" s="56"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="64"/>
+      <c r="Z3" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AB3" s="64"/>
+      <c r="AA3" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="69"/>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13">
         <f>SUM(D5:D6)</f>
         <v>35</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="27">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="28">
         <f t="shared" ref="F4:W4" si="3">SUM(F5:F6)</f>
         <v>3</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="28">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="28">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="28">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="28">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="28">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="28">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P4" s="26">
+      <c r="P4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q4" s="26">
+      <c r="Q4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R4" s="26">
+      <c r="R4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S4" s="26">
+      <c r="S4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T4" s="26">
+      <c r="T4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U4" s="26">
+      <c r="U4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V4" s="26">
+      <c r="V4" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W4" s="34">
+      <c r="W4" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X4" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y4" s="59"/>
-      <c r="Z4" s="65" t="s">
+      <c r="X4" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="AA4" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB4" s="66" t="s">
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="70" t="s">
         <v>13</v>
+      </c>
+      <c r="AA4" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="71" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A5" s="9"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="11">
+      <c r="A5" s="11"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="25">
+      <c r="D5" s="13">
+        <v>15</v>
+      </c>
+      <c r="E5" s="27">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <v>1</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="28">
         <v>1</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="28">
         <v>1</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="28">
         <v>1</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="28">
         <v>1</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="28">
         <v>1</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="28">
         <v>1</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y5" s="59"/>
-      <c r="Z5" s="67" t="s">
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="AA5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB5" s="64" t="s">
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="72" t="s">
         <v>17</v>
+      </c>
+      <c r="AA5" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="69" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="17">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="19">
         <v>20</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="31">
         <v>2</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="32">
         <v>2</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="32">
         <v>2</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="32">
         <v>2</v>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="32">
         <v>2</v>
       </c>
-      <c r="K6" s="30">
+      <c r="K6" s="32">
         <v>2</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="32">
         <v>2</v>
       </c>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA6" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB6" s="59"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA6" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB6" s="64"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="13">
         <f>SUM(D8:D10)</f>
         <v>33</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="27">
         <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="33">
         <f t="shared" ref="F7:W7" si="4">SUM(F8:F10)</f>
         <v>4</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="33">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="33">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="33">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="33">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="33">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="33">
         <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N7" s="31">
+      <c r="N7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O7" s="31">
+      <c r="O7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P7" s="31">
+      <c r="P7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="31">
+      <c r="Q7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R7" s="31">
+      <c r="R7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S7" s="31">
+      <c r="S7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T7" s="31">
+      <c r="T7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="U7" s="31">
+      <c r="U7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V7" s="31">
+      <c r="V7" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W7" s="34">
+      <c r="W7" s="36">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="X7" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y7" s="59"/>
-      <c r="Z7" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA7" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB7" s="59"/>
+      <c r="X7" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA7" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="64"/>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A8" s="9"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="A8" s="11"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="13">
         <v>9</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="27">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="29">
         <v>1</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="28">
         <v>1</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="28">
         <v>1</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="28">
         <v>1</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="28">
         <v>1</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="28">
         <v>1</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="28">
         <v>1</v>
       </c>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y8" s="59"/>
-      <c r="Z8" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA8" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB8" s="59"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="52"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA8" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB8" s="64"/>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A9" s="9"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="11">
+      <c r="A9" s="11"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="13">
         <v>12</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="27">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="29">
         <v>1</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="28">
         <v>1</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="28">
         <v>1</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="28">
         <v>1</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="28">
         <v>1</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="28">
         <v>1</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="28">
         <v>1</v>
       </c>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y9" s="59"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="73"/>
-      <c r="AB9" s="59"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="77"/>
+      <c r="AA9" s="78"/>
+      <c r="AB9" s="64"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="17">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="19">
         <v>12</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="30">
         <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="31">
         <v>2</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="32">
         <v>1</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="32">
         <v>1</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="32">
         <v>1</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="32">
         <v>3</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="32">
         <v>2</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="32">
         <v>1.5</v>
       </c>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y10" s="59"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="64"/>
-      <c r="AB10" s="59"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="77"/>
+      <c r="AA10" s="69"/>
+      <c r="AB10" s="64"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="13">
         <f>SUM(D12:D13)</f>
         <v>15</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="27">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="33">
         <f t="shared" ref="F11:W11" si="5">SUM(F12:F13)</f>
         <v>7</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="33">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="33">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="33">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="31">
+      <c r="M11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="31">
+      <c r="N11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="31">
+      <c r="O11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="31">
+      <c r="P11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="31">
+      <c r="Q11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R11" s="31">
+      <c r="R11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S11" s="31">
+      <c r="S11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T11" s="31">
+      <c r="T11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U11" s="31">
+      <c r="U11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V11" s="31">
+      <c r="V11" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W11" s="34">
+      <c r="W11" s="36">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X11" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="59"/>
-      <c r="Z11" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA11" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB11" s="59"/>
+      <c r="X11" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA11" s="79" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB11" s="64"/>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A12" s="9"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="A12" s="11"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="13">
         <v>3</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="27">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="29">
         <v>3</v>
       </c>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y12" s="59"/>
-      <c r="Z12" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA12" s="68" t="s">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="AB12" s="59"/>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA12" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB12" s="64"/>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="17">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="19">
         <v>12</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="30">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="31">
         <v>4</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="32">
         <v>2</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="32">
         <v>4</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="32">
         <v>2</v>
       </c>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y13" s="59"/>
-      <c r="Z13" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA13" s="76" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB13" s="59"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y13" s="64"/>
+      <c r="Z13" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA13" s="81" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB13" s="64"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13">
         <f>SUM(D15:D16)</f>
         <v>4</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="33">
         <f t="shared" ref="F14:W14" si="6">SUM(F15:F16)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O14" s="31">
+      <c r="O14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P14" s="31">
+      <c r="P14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="31">
+      <c r="Q14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R14" s="31">
+      <c r="R14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S14" s="31">
+      <c r="S14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T14" s="31">
+      <c r="T14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U14" s="31">
+      <c r="U14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V14" s="31">
+      <c r="V14" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W14" s="34">
+      <c r="W14" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X14" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y14" s="59"/>
-      <c r="Z14" s="65" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA14" s="77" t="s">
+      <c r="X14" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y14" s="64"/>
+      <c r="Z14" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="AB14" s="59"/>
+      <c r="AA14" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB14" s="64"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A15" s="9"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="11">
+      <c r="A15" s="11"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="13">
         <v>2</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="26"/>
-      <c r="W15" s="26"/>
-      <c r="X15" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y15" s="59"/>
-      <c r="Z15" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA15" s="70" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB15" s="59"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="52"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA15" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB15" s="64"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="17">
+      <c r="A16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="19">
         <v>2</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F16" s="29"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="55"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y16" s="59"/>
-      <c r="Z16" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA16" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB16" s="59"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y16" s="64"/>
+      <c r="Z16" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA16" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB16" s="64"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A17" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="7">
+      <c r="A17" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="9">
         <f>D17/$D$65</f>
         <v>0.223021582733813</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="10">
         <f>D18+D21+D23+D26</f>
         <v>62</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="25">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="34">
         <f t="shared" ref="F17:V17" si="7">F18+F21+F23+F26</f>
         <v>1</v>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="34">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="34">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="34">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J17" s="32">
+      <c r="J17" s="34">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="K17" s="32">
+      <c r="K17" s="34">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L17" s="32">
+      <c r="L17" s="34">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="M17" s="32">
+      <c r="M17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N17" s="32">
+      <c r="N17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O17" s="32">
+      <c r="O17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P17" s="32">
+      <c r="P17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="32">
+      <c r="Q17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R17" s="32">
+      <c r="R17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S17" s="32">
+      <c r="S17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T17" s="32">
+      <c r="T17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U17" s="32">
+      <c r="U17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="V17" s="32">
+      <c r="V17" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W17" s="56"/>
-      <c r="X17" s="57"/>
-      <c r="Y17" s="59"/>
-      <c r="AA17" s="78"/>
-      <c r="AB17" s="59"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="62"/>
+      <c r="Y17" s="64"/>
+      <c r="AA17" s="83"/>
+      <c r="AB17" s="64"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13">
         <f>SUM(D19:D20)</f>
         <v>4</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="27">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="33">
         <f t="shared" ref="F18:W18" si="8">SUM(F19:F20)</f>
         <v>1</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="33">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M18" s="31">
+      <c r="M18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N18" s="31">
+      <c r="N18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O18" s="31">
+      <c r="O18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P18" s="31">
+      <c r="P18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="31">
+      <c r="Q18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R18" s="31">
+      <c r="R18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S18" s="31">
+      <c r="S18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T18" s="31">
+      <c r="T18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U18" s="31">
+      <c r="U18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V18" s="31">
+      <c r="V18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W18" s="31">
+      <c r="W18" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X18" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y18" s="59"/>
-      <c r="Z18" s="79" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA18" s="79"/>
-      <c r="AB18" s="59"/>
+      <c r="X18" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y18" s="64"/>
+      <c r="Z18" s="84" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="64"/>
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A19" s="9"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="11">
+      <c r="A19" s="11"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="13">
         <v>2</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="27">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="28">
         <v>1</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="35">
         <v>1</v>
       </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-      <c r="V19" s="26"/>
-      <c r="W19" s="26"/>
-      <c r="X19" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y19" s="59"/>
-      <c r="Z19" s="80" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA19" s="80"/>
-      <c r="AB19" s="59"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="52"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y19" s="64"/>
+      <c r="Z19" s="85" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA19" s="85"/>
+      <c r="AB19" s="64"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="17">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="19">
         <v>2</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="30">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F20" s="29"/>
-      <c r="G20" s="30">
+      <c r="F20" s="31"/>
+      <c r="G20" s="32">
         <v>1</v>
       </c>
-      <c r="H20" s="33">
+      <c r="H20" s="35">
         <v>1</v>
       </c>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y20" s="59"/>
-      <c r="Z20" s="80"/>
-      <c r="AA20" s="80"/>
-      <c r="AB20" s="59"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y20" s="64"/>
+      <c r="Z20" s="85"/>
+      <c r="AA20" s="85"/>
+      <c r="AB20" s="64"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="13">
         <v>6</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="27">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="33">
         <f t="shared" ref="F21:W21" si="9">SUM(F22)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X21" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y21" s="59"/>
-      <c r="Z21" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA21" s="81"/>
-      <c r="AB21" s="59"/>
+      <c r="X21" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y21" s="64"/>
+      <c r="Z21" s="86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21" s="86"/>
+      <c r="AB21" s="64"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A22" s="9"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="11">
+      <c r="A22" s="11"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="13">
         <v>6</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="27">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26">
+      <c r="F22" s="29"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28">
         <v>1</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="28">
         <v>1</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="28">
         <v>1</v>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="28">
         <v>1</v>
       </c>
-      <c r="L22" s="26">
+      <c r="L22" s="28">
         <v>1</v>
       </c>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="47"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="26"/>
-      <c r="W22" s="26"/>
-      <c r="X22" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y22" s="59"/>
-      <c r="Z22" s="81"/>
-      <c r="AA22" s="81"/>
-      <c r="AB22" s="59"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y22" s="64"/>
+      <c r="Z22" s="86"/>
+      <c r="AA22" s="86"/>
+      <c r="AB22" s="64"/>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="11">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="13">
         <f>SUM(D24:D25)</f>
         <v>15</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="33">
         <f t="shared" ref="F23:K23" si="10">SUM(F24:F25)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J23" s="34">
+      <c r="J23" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K23" s="34">
+      <c r="K23" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="34"/>
-      <c r="W23" s="34">
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="52"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="36">
         <f>SUM(W24:W25)</f>
         <v>0</v>
       </c>
-      <c r="X23" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y23" s="59"/>
-      <c r="Z23" s="59"/>
-      <c r="AA23" s="59"/>
-      <c r="AB23" s="59"/>
+      <c r="X23" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="64"/>
+      <c r="AA23" s="64"/>
+      <c r="AB23" s="64"/>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A24" s="9"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="11">
+      <c r="A24" s="11"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="13">
         <v>5</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F24" s="27"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="47"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="26"/>
-      <c r="W24" s="26"/>
-      <c r="X24" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y24" s="59"/>
-      <c r="Z24" s="59"/>
-      <c r="AA24" s="59"/>
-      <c r="AB24" s="59"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="49"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="52"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="28"/>
+      <c r="W24" s="28"/>
+      <c r="X24" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y24" s="64"/>
+      <c r="Z24" s="64"/>
+      <c r="AA24" s="64"/>
+      <c r="AB24" s="64"/>
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="17">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="19">
         <v>10</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F25" s="29"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="48"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="38"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
-      <c r="X25" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y25" s="59"/>
-      <c r="Z25" s="59"/>
-      <c r="AA25" s="59"/>
-      <c r="AB25" s="59"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="53"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="40"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
+      <c r="X25" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y25" s="64"/>
+      <c r="Z25" s="64"/>
+      <c r="AA25" s="64"/>
+      <c r="AB25" s="64"/>
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="11">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="13">
         <f>SUM(D27:D28)</f>
         <v>37</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="33">
         <f t="shared" ref="F26:K26" si="11">SUM(F27:F28)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="K26" s="34">
+      <c r="K26" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="47"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="26"/>
-      <c r="W26" s="34">
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="52"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="36">
         <f>SUM(W27:W28)</f>
         <v>0</v>
       </c>
-      <c r="X26" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y26" s="59"/>
-      <c r="Z26" s="59"/>
-      <c r="AA26" s="59"/>
-      <c r="AB26" s="59"/>
+      <c r="X26" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y26" s="64"/>
+      <c r="Z26" s="64"/>
+      <c r="AA26" s="64"/>
+      <c r="AB26" s="64"/>
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A27" s="9"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="11">
+      <c r="A27" s="11"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="13">
         <v>15</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F27" s="27"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="40"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="26"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y27" s="59"/>
-      <c r="Z27" s="59"/>
-      <c r="AA27" s="59"/>
-      <c r="AB27" s="59"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="52"/>
+      <c r="T27" s="42"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y27" s="64"/>
+      <c r="Z27" s="64"/>
+      <c r="AA27" s="64"/>
+      <c r="AB27" s="64"/>
     </row>
     <row r="28" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="17">
+      <c r="A28" s="16"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="19">
         <v>22</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F28" s="29"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y28" s="59"/>
-      <c r="Z28" s="59"/>
-      <c r="AA28" s="59"/>
-      <c r="AB28" s="59"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="40"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y28" s="64"/>
+      <c r="Z28" s="64"/>
+      <c r="AA28" s="64"/>
+      <c r="AB28" s="64"/>
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A29" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="7">
+      <c r="A29" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="20"/>
+      <c r="C29" s="9">
         <f>D29/$D$65</f>
         <v>0.464028776978417</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="10">
         <f>D30+D40+D47+D52+D62</f>
         <v>129</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="25">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="34">
         <f t="shared" ref="F29:V29" si="12">F30+F40+F47+F52+F62</f>
         <v>0</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="34">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="34">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="34">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="J29" s="32">
+      <c r="J29" s="34">
         <f t="shared" si="12"/>
         <v>8</v>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="34">
         <f t="shared" si="12"/>
         <v>15</v>
       </c>
-      <c r="L29" s="32">
+      <c r="L29" s="34">
         <f t="shared" si="12"/>
         <v>8</v>
       </c>
-      <c r="M29" s="32">
+      <c r="M29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R29" s="32">
+      <c r="R29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S29" s="32">
+      <c r="S29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T29" s="32">
+      <c r="T29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U29" s="32">
+      <c r="U29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="V29" s="32">
+      <c r="V29" s="34">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="W29" s="56"/>
-      <c r="X29" s="57"/>
-      <c r="Y29" s="59"/>
-      <c r="Z29" s="59"/>
-      <c r="AA29" s="59"/>
-      <c r="AB29" s="59"/>
+      <c r="W29" s="61"/>
+      <c r="X29" s="62"/>
+      <c r="Y29" s="64"/>
+      <c r="Z29" s="64"/>
+      <c r="AA29" s="64"/>
+      <c r="AB29" s="64"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="11">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="13">
         <f>SUM(D31:D39)</f>
         <v>26</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="27">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="33">
         <f t="shared" ref="F30:W30" si="13">SUM(F31:F39)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="36">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="36">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="36">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="36">
         <f t="shared" si="13"/>
         <v>13</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="36">
         <f t="shared" si="13"/>
         <v>6</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="W30" s="34">
+      <c r="W30" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X30" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y30" s="59"/>
-      <c r="Z30" s="59"/>
-      <c r="AA30" s="59"/>
-      <c r="AB30" s="59"/>
+      <c r="X30" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y30" s="64"/>
+      <c r="Z30" s="64"/>
+      <c r="AA30" s="64"/>
+      <c r="AB30" s="64"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A31" s="9"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="11">
+      <c r="A31" s="11"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="13">
         <v>1</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="27">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F31" s="27"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26">
+      <c r="F31" s="29"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28">
         <v>1</v>
       </c>
-      <c r="I31" s="38">
+      <c r="I31" s="40">
         <v>1</v>
       </c>
-      <c r="J31" s="26">
+      <c r="J31" s="28">
         <v>2</v>
       </c>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="47"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y31" s="59"/>
-      <c r="Z31" s="59"/>
-      <c r="AA31" s="59"/>
-      <c r="AB31" s="59"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="52"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="28"/>
+      <c r="V31" s="28"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y31" s="64"/>
+      <c r="Z31" s="64"/>
+      <c r="AA31" s="64"/>
+      <c r="AB31" s="64"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A32" s="9"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="11">
+      <c r="A32" s="11"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="13">
         <v>2</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="27">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F32" s="27"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="39">
+      <c r="F32" s="29"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="41">
         <v>1</v>
       </c>
-      <c r="J32" s="26">
+      <c r="J32" s="28">
         <v>2</v>
       </c>
-      <c r="K32" s="40"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="47"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="26"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y32" s="59"/>
-      <c r="Z32" s="59"/>
-      <c r="AA32" s="59"/>
-      <c r="AB32" s="59"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y32" s="64"/>
+      <c r="Z32" s="64"/>
+      <c r="AA32" s="64"/>
+      <c r="AB32" s="64"/>
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A33" s="9"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="11">
+      <c r="A33" s="11"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="13">
         <v>4</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="27">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F33" s="27"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="40">
+      <c r="F33" s="29"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="42">
         <v>2</v>
       </c>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="47"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="26"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y33" s="59"/>
-      <c r="Z33" s="59"/>
-      <c r="AA33" s="59"/>
-      <c r="AB33" s="59"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="52"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
+      <c r="V33" s="28"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y33" s="64"/>
+      <c r="Z33" s="64"/>
+      <c r="AA33" s="64"/>
+      <c r="AB33" s="64"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A34" s="9"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="11">
+      <c r="A34" s="11"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="13">
         <v>4</v>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="27">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="40">
+      <c r="F34" s="29"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="42">
         <v>4</v>
       </c>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="26"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y34" s="59"/>
-      <c r="Z34" s="59"/>
-      <c r="AA34" s="59"/>
-      <c r="AB34" s="59"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="52"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="28"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y34" s="64"/>
+      <c r="Z34" s="64"/>
+      <c r="AA34" s="64"/>
+      <c r="AB34" s="64"/>
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A35" s="9"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="11">
+      <c r="A35" s="11"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" s="13">
         <v>4</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="27">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F35" s="27"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="40">
+      <c r="F35" s="29"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="42">
         <v>4</v>
       </c>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="26"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y35" s="59"/>
-      <c r="Z35" s="59"/>
-      <c r="AA35" s="59"/>
-      <c r="AB35" s="59"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y35" s="64"/>
+      <c r="Z35" s="64"/>
+      <c r="AA35" s="64"/>
+      <c r="AB35" s="64"/>
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A36" s="9"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" s="11">
+      <c r="A36" s="11"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="13">
         <v>4</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="27">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="40">
+      <c r="F36" s="29"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="42">
         <v>2</v>
       </c>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="47"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="26"/>
-      <c r="W36" s="26"/>
-      <c r="X36" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y36" s="59"/>
-      <c r="Z36" s="59"/>
-      <c r="AA36" s="59"/>
-      <c r="AB36" s="59"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="52"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="28"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y36" s="64"/>
+      <c r="Z36" s="64"/>
+      <c r="AA36" s="64"/>
+      <c r="AB36" s="64"/>
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A37" s="9"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" s="11">
+      <c r="A37" s="11"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="13">
         <v>2</v>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="27">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F37" s="27"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="40">
+      <c r="F37" s="29"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="42">
         <v>1</v>
       </c>
-      <c r="L37" s="26">
+      <c r="L37" s="28">
         <v>1</v>
       </c>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="47"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
-      <c r="V37" s="26"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y37" s="59"/>
-      <c r="Z37" s="59"/>
-      <c r="AA37" s="59"/>
-      <c r="AB37" s="59"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="52"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y37" s="64"/>
+      <c r="Z37" s="64"/>
+      <c r="AA37" s="64"/>
+      <c r="AB37" s="64"/>
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A38" s="9"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="11">
+      <c r="A38" s="11"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="13">
         <v>3</v>
       </c>
-      <c r="E38" s="25">
+      <c r="E38" s="27">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="40">
+      <c r="F38" s="29"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="42">
         <v>3</v>
       </c>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="47"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="26"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y38" s="59"/>
-      <c r="Z38" s="59"/>
-      <c r="AA38" s="59"/>
-      <c r="AB38" s="59"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
+      <c r="V38" s="28"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y38" s="64"/>
+      <c r="Z38" s="64"/>
+      <c r="AA38" s="64"/>
+      <c r="AB38" s="64"/>
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A39" s="9"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" s="11">
+      <c r="A39" s="11"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="13">
         <v>2</v>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="27">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F39" s="27"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="40">
+      <c r="F39" s="29"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="42">
         <v>2</v>
       </c>
-      <c r="M39" s="26"/>
-      <c r="N39" s="26"/>
-      <c r="O39" s="26"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="47"/>
-      <c r="T39" s="26"/>
-      <c r="U39" s="26"/>
-      <c r="V39" s="26"/>
-      <c r="W39" s="26"/>
-      <c r="X39" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y39" s="59"/>
-      <c r="Z39" s="59"/>
-      <c r="AA39" s="59"/>
-      <c r="AB39" s="59"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="52"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y39" s="64"/>
+      <c r="Z39" s="64"/>
+      <c r="AA39" s="64"/>
+      <c r="AB39" s="64"/>
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A40" s="9"/>
-      <c r="B40" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11">
+      <c r="A40" s="11"/>
+      <c r="B40" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="12"/>
+      <c r="D40" s="13">
         <f>SUM(D41:D46)</f>
         <v>15</v>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="27">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="33">
         <f t="shared" ref="F40:W40" si="14">SUM(F41:F46)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="34">
+      <c r="G40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H40" s="34">
+      <c r="H40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I40" s="34">
+      <c r="I40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J40" s="34">
+      <c r="J40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K40" s="34">
+      <c r="K40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L40" s="34">
+      <c r="L40" s="36">
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="M40" s="34">
+      <c r="M40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N40" s="34">
+      <c r="N40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O40" s="34">
+      <c r="O40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="P40" s="34">
+      <c r="P40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Q40" s="34">
+      <c r="Q40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R40" s="34">
+      <c r="R40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S40" s="34">
+      <c r="S40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="T40" s="34">
+      <c r="T40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="U40" s="34">
+      <c r="U40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="V40" s="34">
+      <c r="V40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W40" s="34">
+      <c r="W40" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="X40" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y40" s="59"/>
-      <c r="Z40" s="59"/>
-      <c r="AA40" s="59"/>
-      <c r="AB40" s="59"/>
+      <c r="X40" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y40" s="64"/>
+      <c r="Z40" s="64"/>
+      <c r="AA40" s="64"/>
+      <c r="AB40" s="64"/>
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A41" s="9"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="11">
+      <c r="A41" s="11"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="13">
         <v>1</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="27">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F41" s="27"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="40">
+      <c r="F41" s="29"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="42">
         <v>2</v>
       </c>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
-      <c r="P41" s="26"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="26"/>
-      <c r="S41" s="47"/>
-      <c r="T41" s="26"/>
-      <c r="U41" s="26"/>
-      <c r="V41" s="26"/>
-      <c r="W41" s="26"/>
-      <c r="X41" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y41" s="59"/>
-      <c r="Z41" s="59"/>
-      <c r="AA41" s="59"/>
-      <c r="AB41" s="59"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="52"/>
+      <c r="T41" s="28"/>
+      <c r="U41" s="28"/>
+      <c r="V41" s="28"/>
+      <c r="W41" s="28"/>
+      <c r="X41" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y41" s="64"/>
+      <c r="Z41" s="64"/>
+      <c r="AA41" s="64"/>
+      <c r="AB41" s="64"/>
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A42" s="9"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D42" s="11">
+      <c r="A42" s="11"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="13">
         <v>2</v>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F42" s="27"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="40"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="47"/>
-      <c r="T42" s="26"/>
-      <c r="U42" s="26"/>
-      <c r="V42" s="26"/>
-      <c r="W42" s="26"/>
-      <c r="X42" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y42" s="59"/>
-      <c r="Z42" s="59"/>
-      <c r="AA42" s="59"/>
-      <c r="AB42" s="59"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y42" s="64"/>
+      <c r="Z42" s="64"/>
+      <c r="AA42" s="64"/>
+      <c r="AB42" s="64"/>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A43" s="9"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D43" s="11">
+      <c r="A43" s="11"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="13">
         <v>5</v>
       </c>
-      <c r="E43" s="25">
+      <c r="E43" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F43" s="27"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
-      <c r="M43" s="40"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="26"/>
-      <c r="U43" s="26"/>
-      <c r="V43" s="26"/>
-      <c r="W43" s="26"/>
-      <c r="X43" s="58"/>
-      <c r="Y43" s="59"/>
-      <c r="Z43" s="59"/>
-      <c r="AA43" s="59"/>
-      <c r="AB43" s="59"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="42"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="52"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="63"/>
+      <c r="Y43" s="64"/>
+      <c r="Z43" s="64"/>
+      <c r="AA43" s="64"/>
+      <c r="AB43" s="64"/>
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A44" s="9"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="11">
+      <c r="A44" s="11"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="13">
         <v>2</v>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F44" s="27"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="40"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="26"/>
-      <c r="Q44" s="26"/>
-      <c r="R44" s="26"/>
-      <c r="S44" s="47"/>
-      <c r="T44" s="26"/>
-      <c r="U44" s="26"/>
-      <c r="V44" s="26"/>
-      <c r="W44" s="26"/>
-      <c r="X44" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y44" s="59"/>
-      <c r="Z44" s="59"/>
-      <c r="AA44" s="59"/>
-      <c r="AB44" s="59"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="42"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="28"/>
+      <c r="R44" s="28"/>
+      <c r="S44" s="52"/>
+      <c r="T44" s="28"/>
+      <c r="U44" s="28"/>
+      <c r="V44" s="28"/>
+      <c r="W44" s="28"/>
+      <c r="X44" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y44" s="64"/>
+      <c r="Z44" s="64"/>
+      <c r="AA44" s="64"/>
+      <c r="AB44" s="64"/>
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A45" s="9"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D45" s="11">
+      <c r="A45" s="11"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="13">
         <v>3</v>
       </c>
-      <c r="E45" s="25">
+      <c r="E45" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F45" s="27"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26"/>
-      <c r="N45" s="40"/>
-      <c r="O45" s="26"/>
-      <c r="P45" s="26"/>
-      <c r="Q45" s="26"/>
-      <c r="R45" s="26"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="26"/>
-      <c r="U45" s="26"/>
-      <c r="V45" s="26"/>
-      <c r="W45" s="26"/>
-      <c r="X45" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y45" s="59"/>
-      <c r="Z45" s="59"/>
-      <c r="AA45" s="59"/>
-      <c r="AB45" s="59"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="42"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="28"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="28"/>
+      <c r="W45" s="28"/>
+      <c r="X45" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y45" s="64"/>
+      <c r="Z45" s="64"/>
+      <c r="AA45" s="64"/>
+      <c r="AB45" s="64"/>
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A46" s="14"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D46" s="17">
+      <c r="A46" s="16"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="19">
         <v>2</v>
       </c>
-      <c r="E46" s="28">
+      <c r="E46" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F46" s="29"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="46"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="48"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y46" s="59"/>
-      <c r="Z46" s="59"/>
-      <c r="AA46" s="59"/>
-      <c r="AB46" s="59"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="50"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="53"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="32"/>
+      <c r="X46" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y46" s="64"/>
+      <c r="Z46" s="64"/>
+      <c r="AA46" s="64"/>
+      <c r="AB46" s="64"/>
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A47" s="9"/>
-      <c r="B47" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="11">
+      <c r="A47" s="11"/>
+      <c r="B47" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="12"/>
+      <c r="D47" s="13">
         <f>SUM(D48:D51)</f>
         <v>31</v>
       </c>
-      <c r="E47" s="25">
+      <c r="E47" s="27">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="33">
         <f t="shared" ref="F47:W47" si="15">SUM(F48:F51)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="36">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="H47" s="34">
+      <c r="H47" s="36">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="I47" s="34">
+      <c r="I47" s="36">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="J47" s="34">
+      <c r="J47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K47" s="34">
+      <c r="K47" s="36">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="L47" s="34">
+      <c r="L47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="M47" s="34">
+      <c r="M47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N47" s="34">
+      <c r="N47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="O47" s="34">
+      <c r="O47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="P47" s="34">
+      <c r="P47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="34">
+      <c r="Q47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="R47" s="34">
+      <c r="R47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="S47" s="34">
+      <c r="S47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="T47" s="34">
+      <c r="T47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="U47" s="34">
+      <c r="U47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="V47" s="34">
+      <c r="V47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="W47" s="34">
+      <c r="W47" s="36">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="X47" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y47" s="59"/>
-      <c r="Z47" s="59"/>
-      <c r="AA47" s="59"/>
-      <c r="AB47" s="59"/>
+      <c r="X47" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y47" s="64"/>
+      <c r="Z47" s="64"/>
+      <c r="AA47" s="64"/>
+      <c r="AB47" s="64"/>
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A48" s="9"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="11">
+      <c r="A48" s="11"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="13">
         <v>8</v>
       </c>
-      <c r="E48" s="25">
+      <c r="E48" s="27">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F48" s="27"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26">
+      <c r="F48" s="29"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28">
         <v>1</v>
       </c>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26"/>
-      <c r="L48" s="26"/>
-      <c r="M48" s="38"/>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="26"/>
-      <c r="Q48" s="26"/>
-      <c r="R48" s="26"/>
-      <c r="S48" s="47"/>
-      <c r="T48" s="26"/>
-      <c r="U48" s="26"/>
-      <c r="V48" s="26"/>
-      <c r="W48" s="26"/>
-      <c r="X48" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y48" s="59"/>
-      <c r="Z48" s="59"/>
-      <c r="AA48" s="59"/>
-      <c r="AB48" s="59"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="40"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="52"/>
+      <c r="T48" s="28"/>
+      <c r="U48" s="28"/>
+      <c r="V48" s="28"/>
+      <c r="W48" s="28"/>
+      <c r="X48" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y48" s="64"/>
+      <c r="Z48" s="64"/>
+      <c r="AA48" s="64"/>
+      <c r="AB48" s="64"/>
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A49" s="9"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D49" s="11">
+      <c r="A49" s="11"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D49" s="13">
         <v>5</v>
       </c>
-      <c r="E49" s="25">
+      <c r="E49" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F49" s="27"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-      <c r="M49" s="38"/>
-      <c r="N49" s="26"/>
-      <c r="O49" s="26"/>
-      <c r="P49" s="26"/>
-      <c r="Q49" s="26"/>
-      <c r="R49" s="26"/>
-      <c r="S49" s="47"/>
-      <c r="T49" s="26"/>
-      <c r="U49" s="26"/>
-      <c r="V49" s="26"/>
-      <c r="W49" s="26"/>
-      <c r="X49" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y49" s="59"/>
-      <c r="Z49" s="59"/>
-      <c r="AA49" s="59"/>
-      <c r="AB49" s="59"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="40"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="52"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y49" s="64"/>
+      <c r="Z49" s="64"/>
+      <c r="AA49" s="64"/>
+      <c r="AB49" s="64"/>
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A50" s="9"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D50" s="11">
+      <c r="A50" s="11"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D50" s="13">
         <v>8</v>
       </c>
-      <c r="E50" s="25">
+      <c r="E50" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F50" s="27"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
-      <c r="M50" s="39"/>
-      <c r="N50" s="40"/>
-      <c r="O50" s="26"/>
-      <c r="P50" s="26"/>
-      <c r="Q50" s="26"/>
-      <c r="R50" s="26"/>
-      <c r="S50" s="47"/>
-      <c r="T50" s="26"/>
-      <c r="U50" s="26"/>
-      <c r="V50" s="26"/>
-      <c r="W50" s="26"/>
-      <c r="X50" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y50" s="59"/>
-      <c r="Z50" s="59"/>
-      <c r="AA50" s="59"/>
-      <c r="AB50" s="59"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="41"/>
+      <c r="N50" s="42"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="28"/>
+      <c r="R50" s="28"/>
+      <c r="S50" s="52"/>
+      <c r="T50" s="28"/>
+      <c r="U50" s="28"/>
+      <c r="V50" s="28"/>
+      <c r="W50" s="28"/>
+      <c r="X50" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y50" s="64"/>
+      <c r="Z50" s="64"/>
+      <c r="AA50" s="64"/>
+      <c r="AB50" s="64"/>
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A51" s="14"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D51" s="17">
+      <c r="A51" s="16"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="19">
         <v>10</v>
       </c>
-      <c r="E51" s="28">
+      <c r="E51" s="30">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F51" s="29"/>
-      <c r="G51" s="30">
+      <c r="F51" s="31"/>
+      <c r="G51" s="32">
         <v>2</v>
       </c>
-      <c r="H51" s="30">
+      <c r="H51" s="32">
         <v>2</v>
       </c>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30">
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32">
         <v>2</v>
       </c>
-      <c r="L51" s="30"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="41"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="30"/>
-      <c r="Q51" s="30"/>
-      <c r="R51" s="30"/>
-      <c r="S51" s="48"/>
-      <c r="T51" s="30"/>
-      <c r="U51" s="30"/>
-      <c r="V51" s="30"/>
-      <c r="W51" s="30"/>
-      <c r="X51" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y51" s="59"/>
-      <c r="Z51" s="59"/>
-      <c r="AA51" s="59"/>
-      <c r="AB51" s="59"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="43"/>
+      <c r="O51" s="50"/>
+      <c r="P51" s="32"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="53"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="32"/>
+      <c r="X51" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y51" s="64"/>
+      <c r="Z51" s="64"/>
+      <c r="AA51" s="64"/>
+      <c r="AB51" s="64"/>
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A52" s="9"/>
-      <c r="B52" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11">
+      <c r="A52" s="11"/>
+      <c r="B52" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="13">
         <f>SUM(D53:D61)</f>
         <v>37</v>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F52" s="31">
+      <c r="F52" s="33">
         <f t="shared" ref="F52:W52" si="16">SUM(F53:F61)</f>
         <v>0</v>
       </c>
-      <c r="G52" s="34">
+      <c r="G52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H52" s="34">
+      <c r="H52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I52" s="34">
+      <c r="I52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J52" s="34">
+      <c r="J52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K52" s="34">
+      <c r="K52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L52" s="34">
+      <c r="L52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M52" s="34">
+      <c r="M52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="N52" s="34">
+      <c r="N52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O52" s="34">
+      <c r="O52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="P52" s="26">
+      <c r="P52" s="28">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q52" s="34">
+      <c r="Q52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="R52" s="26">
+      <c r="R52" s="28">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="S52" s="47">
+      <c r="S52" s="52">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="T52" s="26">
+      <c r="T52" s="28">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="U52" s="26">
+      <c r="U52" s="28">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="V52" s="26">
+      <c r="V52" s="28">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="W52" s="34">
+      <c r="W52" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X52" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y52" s="59"/>
-      <c r="Z52" s="59"/>
-      <c r="AA52" s="59"/>
-      <c r="AB52" s="59"/>
+      <c r="X52" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y52" s="64"/>
+      <c r="Z52" s="64"/>
+      <c r="AA52" s="64"/>
+      <c r="AB52" s="64"/>
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A53" s="9"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D53" s="11">
+      <c r="A53" s="11"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" s="13">
         <v>2</v>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F53" s="27"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-      <c r="M53" s="26"/>
-      <c r="N53" s="26"/>
-      <c r="O53" s="40"/>
-      <c r="P53" s="26"/>
-      <c r="Q53" s="26"/>
-      <c r="R53" s="26"/>
-      <c r="S53" s="47"/>
-      <c r="T53" s="26"/>
-      <c r="U53" s="26"/>
-      <c r="V53" s="26"/>
-      <c r="W53" s="26"/>
-      <c r="X53" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y53" s="59"/>
-      <c r="Z53" s="59"/>
-      <c r="AA53" s="59"/>
-      <c r="AB53" s="59"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="28"/>
+      <c r="K53" s="28"/>
+      <c r="L53" s="28"/>
+      <c r="M53" s="28"/>
+      <c r="N53" s="28"/>
+      <c r="O53" s="42"/>
+      <c r="P53" s="28"/>
+      <c r="Q53" s="28"/>
+      <c r="R53" s="28"/>
+      <c r="S53" s="52"/>
+      <c r="T53" s="28"/>
+      <c r="U53" s="28"/>
+      <c r="V53" s="28"/>
+      <c r="W53" s="28"/>
+      <c r="X53" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y53" s="64"/>
+      <c r="Z53" s="64"/>
+      <c r="AA53" s="64"/>
+      <c r="AB53" s="64"/>
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A54" s="9"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" s="11">
+      <c r="A54" s="11"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54" s="13">
         <v>5</v>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F54" s="27"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
-      <c r="M54" s="26"/>
-      <c r="N54" s="26"/>
-      <c r="O54" s="26"/>
-      <c r="P54" s="40"/>
-      <c r="Q54" s="26"/>
-      <c r="R54" s="26"/>
-      <c r="S54" s="47"/>
-      <c r="T54" s="26"/>
-      <c r="U54" s="26"/>
-      <c r="V54" s="26"/>
-      <c r="W54" s="26"/>
-      <c r="X54" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y54" s="59"/>
-      <c r="Z54" s="59"/>
-      <c r="AA54" s="59"/>
-      <c r="AB54" s="59"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="28"/>
+      <c r="R54" s="28"/>
+      <c r="S54" s="52"/>
+      <c r="T54" s="28"/>
+      <c r="U54" s="28"/>
+      <c r="V54" s="28"/>
+      <c r="W54" s="28"/>
+      <c r="X54" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y54" s="64"/>
+      <c r="Z54" s="64"/>
+      <c r="AA54" s="64"/>
+      <c r="AB54" s="64"/>
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A55" s="9"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D55" s="11">
+      <c r="A55" s="11"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="13">
         <v>5</v>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F55" s="27"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55" s="26"/>
-      <c r="N55" s="26"/>
-      <c r="O55" s="26"/>
-      <c r="P55" s="40"/>
-      <c r="Q55" s="26"/>
-      <c r="R55" s="26"/>
-      <c r="S55" s="47"/>
-      <c r="T55" s="26"/>
-      <c r="U55" s="26"/>
-      <c r="V55" s="26"/>
-      <c r="W55" s="26"/>
-      <c r="X55" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y55" s="59"/>
-      <c r="Z55" s="59"/>
-      <c r="AA55" s="59"/>
-      <c r="AB55" s="59"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="42"/>
+      <c r="Q55" s="28"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="52"/>
+      <c r="T55" s="28"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="28"/>
+      <c r="W55" s="28"/>
+      <c r="X55" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y55" s="64"/>
+      <c r="Z55" s="64"/>
+      <c r="AA55" s="64"/>
+      <c r="AB55" s="64"/>
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A56" s="9"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D56" s="11">
+      <c r="A56" s="11"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="13">
         <v>5</v>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F56" s="27"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
-      <c r="M56" s="26"/>
-      <c r="N56" s="26"/>
-      <c r="O56" s="26"/>
-      <c r="P56" s="26"/>
-      <c r="Q56" s="40"/>
-      <c r="R56" s="26"/>
-      <c r="S56" s="47"/>
-      <c r="T56" s="26"/>
-      <c r="U56" s="26"/>
-      <c r="V56" s="26"/>
-      <c r="W56" s="26"/>
-      <c r="X56" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y56" s="59"/>
-      <c r="Z56" s="59"/>
-      <c r="AA56" s="59"/>
-      <c r="AB56" s="59"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="28"/>
+      <c r="O56" s="28"/>
+      <c r="P56" s="28"/>
+      <c r="Q56" s="42"/>
+      <c r="R56" s="28"/>
+      <c r="S56" s="52"/>
+      <c r="T56" s="28"/>
+      <c r="U56" s="28"/>
+      <c r="V56" s="28"/>
+      <c r="W56" s="28"/>
+      <c r="X56" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y56" s="64"/>
+      <c r="Z56" s="64"/>
+      <c r="AA56" s="64"/>
+      <c r="AB56" s="64"/>
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A57" s="9"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D57" s="11">
+      <c r="A57" s="11"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="13">
         <v>3</v>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F57" s="27"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="26"/>
-      <c r="K57" s="26"/>
-      <c r="L57" s="26"/>
-      <c r="M57" s="26"/>
-      <c r="N57" s="26"/>
-      <c r="O57" s="26"/>
-      <c r="P57" s="26"/>
-      <c r="Q57" s="40"/>
-      <c r="R57" s="26"/>
-      <c r="S57" s="47"/>
-      <c r="T57" s="26"/>
-      <c r="U57" s="26"/>
-      <c r="V57" s="26"/>
-      <c r="W57" s="26"/>
-      <c r="X57" s="53"/>
-      <c r="Y57" s="59"/>
-      <c r="Z57" s="59"/>
-      <c r="AA57" s="59"/>
-      <c r="AB57" s="59"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+      <c r="P57" s="28"/>
+      <c r="Q57" s="42"/>
+      <c r="R57" s="28"/>
+      <c r="S57" s="52"/>
+      <c r="T57" s="28"/>
+      <c r="U57" s="28"/>
+      <c r="V57" s="28"/>
+      <c r="W57" s="28"/>
+      <c r="X57" s="58"/>
+      <c r="Y57" s="64"/>
+      <c r="Z57" s="64"/>
+      <c r="AA57" s="64"/>
+      <c r="AB57" s="64"/>
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A58" s="9"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" s="11">
+      <c r="A58" s="11"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="13">
         <v>3</v>
       </c>
-      <c r="E58" s="25">
+      <c r="E58" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F58" s="27"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="26"/>
-      <c r="M58" s="26"/>
-      <c r="N58" s="26"/>
-      <c r="O58" s="26"/>
-      <c r="P58" s="26"/>
-      <c r="Q58" s="26"/>
-      <c r="R58" s="40"/>
-      <c r="S58" s="47"/>
-      <c r="T58" s="26"/>
-      <c r="U58" s="26"/>
-      <c r="V58" s="26"/>
-      <c r="W58" s="26"/>
-      <c r="X58" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y58" s="59"/>
-      <c r="Z58" s="59"/>
-      <c r="AA58" s="59"/>
-      <c r="AB58" s="59"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="Q58" s="28"/>
+      <c r="R58" s="42"/>
+      <c r="S58" s="52"/>
+      <c r="T58" s="28"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="28"/>
+      <c r="W58" s="28"/>
+      <c r="X58" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y58" s="64"/>
+      <c r="Z58" s="64"/>
+      <c r="AA58" s="64"/>
+      <c r="AB58" s="64"/>
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A59" s="9"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D59" s="11">
+      <c r="A59" s="11"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="13">
         <v>6</v>
       </c>
-      <c r="E59" s="25">
+      <c r="E59" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F59" s="27"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="26"/>
-      <c r="I59" s="26"/>
-      <c r="J59" s="26"/>
-      <c r="K59" s="26"/>
-      <c r="L59" s="26"/>
-      <c r="M59" s="26"/>
-      <c r="N59" s="26"/>
-      <c r="O59" s="26"/>
-      <c r="P59" s="26"/>
-      <c r="Q59" s="26"/>
-      <c r="R59" s="40"/>
-      <c r="S59" s="47"/>
-      <c r="T59" s="26"/>
-      <c r="U59" s="26"/>
-      <c r="V59" s="26"/>
-      <c r="W59" s="26"/>
-      <c r="X59" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y59" s="59"/>
-      <c r="Z59" s="59"/>
-      <c r="AA59" s="59"/>
-      <c r="AB59" s="59"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="28"/>
+      <c r="O59" s="28"/>
+      <c r="P59" s="28"/>
+      <c r="Q59" s="28"/>
+      <c r="R59" s="42"/>
+      <c r="S59" s="52"/>
+      <c r="T59" s="28"/>
+      <c r="U59" s="28"/>
+      <c r="V59" s="28"/>
+      <c r="W59" s="28"/>
+      <c r="X59" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y59" s="64"/>
+      <c r="Z59" s="64"/>
+      <c r="AA59" s="64"/>
+      <c r="AB59" s="64"/>
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A60" s="9"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60" s="11">
+      <c r="A60" s="11"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="13">
         <v>5</v>
       </c>
-      <c r="E60" s="25">
+      <c r="E60" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F60" s="27"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="26"/>
-      <c r="K60" s="26"/>
-      <c r="L60" s="26"/>
-      <c r="M60" s="26"/>
-      <c r="N60" s="26"/>
-      <c r="O60" s="26"/>
-      <c r="P60" s="26"/>
-      <c r="Q60" s="26"/>
-      <c r="R60" s="26"/>
-      <c r="S60" s="47"/>
-      <c r="T60" s="40"/>
-      <c r="U60" s="26"/>
-      <c r="V60" s="26"/>
-      <c r="W60" s="26"/>
-      <c r="X60" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y60" s="59"/>
-      <c r="Z60" s="59"/>
-      <c r="AA60" s="59"/>
-      <c r="AB60" s="59"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="28"/>
+      <c r="N60" s="28"/>
+      <c r="O60" s="28"/>
+      <c r="P60" s="28"/>
+      <c r="Q60" s="28"/>
+      <c r="R60" s="28"/>
+      <c r="S60" s="52"/>
+      <c r="T60" s="42"/>
+      <c r="U60" s="28"/>
+      <c r="V60" s="28"/>
+      <c r="W60" s="28"/>
+      <c r="X60" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y60" s="64"/>
+      <c r="Z60" s="64"/>
+      <c r="AA60" s="64"/>
+      <c r="AB60" s="64"/>
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A61" s="9"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" s="11">
+      <c r="A61" s="11"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="13">
         <v>3</v>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F61" s="27"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
-      <c r="R61" s="26"/>
-      <c r="S61" s="47"/>
-      <c r="T61" s="40"/>
-      <c r="U61" s="26"/>
-      <c r="V61" s="26"/>
-      <c r="W61" s="26"/>
-      <c r="X61" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y61" s="59"/>
-      <c r="Z61" s="59"/>
-      <c r="AA61" s="59"/>
-      <c r="AB61" s="59"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+      <c r="P61" s="28"/>
+      <c r="Q61" s="28"/>
+      <c r="R61" s="28"/>
+      <c r="S61" s="52"/>
+      <c r="T61" s="42"/>
+      <c r="U61" s="28"/>
+      <c r="V61" s="28"/>
+      <c r="W61" s="28"/>
+      <c r="X61" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y61" s="64"/>
+      <c r="Z61" s="64"/>
+      <c r="AA61" s="64"/>
+      <c r="AB61" s="64"/>
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A62" s="9"/>
-      <c r="B62" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="11">
+      <c r="A62" s="11"/>
+      <c r="B62" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="12"/>
+      <c r="D62" s="13">
         <f>SUM(D63:D64)</f>
         <v>20</v>
       </c>
-      <c r="E62" s="25">
+      <c r="E62" s="27">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="33">
         <f t="shared" ref="F62:W62" si="17">SUM(F63:F64)</f>
         <v>0</v>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="36">
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="36">
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="K62" s="34">
+      <c r="K62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="O62" s="34">
+      <c r="O62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P62" s="26">
+      <c r="P62" s="28">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="Q62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R62" s="26">
+      <c r="R62" s="28">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="S62" s="47">
+      <c r="S62" s="52">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T62" s="26">
+      <c r="T62" s="28">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="U62" s="26">
+      <c r="U62" s="28">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="V62" s="26">
+      <c r="V62" s="28">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="W62" s="34">
+      <c r="W62" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X62" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y62" s="59"/>
-      <c r="Z62" s="59"/>
-      <c r="AA62" s="59"/>
-      <c r="AB62" s="59"/>
+      <c r="X62" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y62" s="64"/>
+      <c r="Z62" s="64"/>
+      <c r="AA62" s="64"/>
+      <c r="AB62" s="64"/>
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A63" s="9"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D63" s="11">
+      <c r="A63" s="11"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="13">
         <v>5</v>
       </c>
-      <c r="E63" s="25">
+      <c r="E63" s="27">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F63" s="27"/>
-      <c r="G63" s="26"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26">
+      <c r="F63" s="29"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28">
         <v>2</v>
       </c>
-      <c r="J63" s="26">
+      <c r="J63" s="28">
         <v>2</v>
       </c>
-      <c r="K63" s="26"/>
-      <c r="L63" s="26"/>
-      <c r="M63" s="26"/>
-      <c r="N63" s="26"/>
-      <c r="O63" s="26"/>
-      <c r="P63" s="26"/>
-      <c r="Q63" s="26"/>
-      <c r="R63" s="26"/>
-      <c r="S63" s="47"/>
-      <c r="T63" s="26"/>
-      <c r="U63" s="26"/>
-      <c r="V63" s="26"/>
-      <c r="W63" s="26"/>
-      <c r="X63" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y63" s="59"/>
-      <c r="Z63" s="59"/>
-      <c r="AA63" s="59"/>
-      <c r="AB63" s="59"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="M63" s="28"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+      <c r="P63" s="28"/>
+      <c r="Q63" s="28"/>
+      <c r="R63" s="28"/>
+      <c r="S63" s="52"/>
+      <c r="T63" s="28"/>
+      <c r="U63" s="28"/>
+      <c r="V63" s="28"/>
+      <c r="W63" s="28"/>
+      <c r="X63" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y63" s="64"/>
+      <c r="Z63" s="64"/>
+      <c r="AA63" s="64"/>
+      <c r="AB63" s="64"/>
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:28">
-      <c r="A64" s="9"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D64" s="11">
+      <c r="A64" s="11"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D64" s="13">
         <v>15</v>
       </c>
-      <c r="E64" s="25">
+      <c r="E64" s="27">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F64" s="27"/>
-      <c r="G64" s="26"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="26">
+      <c r="F64" s="29"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28">
         <v>2</v>
       </c>
-      <c r="J64" s="26">
+      <c r="J64" s="28">
         <v>2</v>
       </c>
-      <c r="K64" s="26"/>
-      <c r="L64" s="26"/>
-      <c r="M64" s="26"/>
-      <c r="N64" s="26"/>
-      <c r="O64" s="26"/>
-      <c r="P64" s="26"/>
-      <c r="Q64" s="26"/>
-      <c r="R64" s="26"/>
-      <c r="S64" s="47"/>
-      <c r="T64" s="26"/>
-      <c r="U64" s="26"/>
-      <c r="V64" s="26"/>
-      <c r="W64" s="26"/>
-      <c r="X64" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y64" s="59"/>
-      <c r="Z64" s="59"/>
-      <c r="AA64" s="59"/>
-      <c r="AB64" s="59"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="28"/>
+      <c r="R64" s="28"/>
+      <c r="S64" s="52"/>
+      <c r="T64" s="28"/>
+      <c r="U64" s="28"/>
+      <c r="V64" s="28"/>
+      <c r="W64" s="28"/>
+      <c r="X64" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y64" s="64"/>
+      <c r="Z64" s="64"/>
+      <c r="AA64" s="64"/>
+      <c r="AB64" s="64"/>
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="2:28">
-      <c r="B65" s="82" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" s="82"/>
-      <c r="D65" s="83">
+      <c r="B65" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" s="87"/>
+      <c r="D65" s="88">
         <f t="shared" ref="D65:V65" si="18">D29+D17+D3</f>
         <v>278</v>
       </c>
-      <c r="E65" s="83">
+      <c r="E65" s="88">
         <f t="shared" si="18"/>
         <v>113.5</v>
       </c>
-      <c r="F65" s="83">
+      <c r="F65" s="88">
         <f t="shared" si="18"/>
         <v>15</v>
       </c>
-      <c r="G65" s="83">
+      <c r="G65" s="88">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="H65" s="83">
+      <c r="H65" s="88">
         <f t="shared" si="18"/>
         <v>15</v>
       </c>
-      <c r="I65" s="83">
+      <c r="I65" s="88">
         <f t="shared" si="18"/>
         <v>16</v>
       </c>
-      <c r="J65" s="83">
+      <c r="J65" s="88">
         <f t="shared" si="18"/>
         <v>17</v>
       </c>
-      <c r="K65" s="83">
+      <c r="K65" s="88">
         <f t="shared" si="18"/>
         <v>23</v>
       </c>
-      <c r="L65" s="83">
+      <c r="L65" s="88">
         <f t="shared" si="18"/>
         <v>15.5</v>
       </c>
-      <c r="M65" s="83">
+      <c r="M65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="N65" s="83">
+      <c r="N65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O65" s="83">
+      <c r="O65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="P65" s="83">
+      <c r="P65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q65" s="83">
+      <c r="Q65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="R65" s="83">
+      <c r="R65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="S65" s="83">
+      <c r="S65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="T65" s="83">
+      <c r="T65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U65" s="83">
+      <c r="U65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="V65" s="83">
+      <c r="V65" s="88">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="W65" s="83"/>
-      <c r="X65" s="86"/>
-      <c r="Y65" s="59"/>
-      <c r="Z65" s="59"/>
-      <c r="AA65" s="59"/>
-      <c r="AB65" s="59"/>
+      <c r="W65" s="88"/>
+      <c r="X65" s="91"/>
+      <c r="Y65" s="64"/>
+      <c r="Z65" s="64"/>
+      <c r="AA65" s="64"/>
+      <c r="AB65" s="64"/>
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="3:28">
-      <c r="C66" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D66" s="84">
+      <c r="C66" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" s="89">
         <f>SUM(F66:V66)</f>
         <v>240</v>
       </c>
-      <c r="E66" s="84">
+      <c r="E66" s="89">
         <f>SUM(F66:V66)</f>
         <v>240</v>
       </c>
-      <c r="F66" s="85">
+      <c r="F66" s="90">
         <v>15</v>
       </c>
-      <c r="G66" s="85">
+      <c r="G66" s="90">
         <v>15</v>
       </c>
-      <c r="H66" s="85">
+      <c r="H66" s="90">
         <v>15</v>
       </c>
-      <c r="I66" s="85">
+      <c r="I66" s="90">
         <v>15</v>
       </c>
-      <c r="J66" s="85">
+      <c r="J66" s="90">
         <v>15</v>
       </c>
-      <c r="K66" s="85">
+      <c r="K66" s="90">
         <v>15</v>
       </c>
-      <c r="L66" s="85">
+      <c r="L66" s="90">
         <v>15</v>
       </c>
-      <c r="M66" s="85">
+      <c r="M66" s="90">
         <v>15</v>
       </c>
-      <c r="N66" s="85">
+      <c r="N66" s="90">
         <v>15</v>
       </c>
-      <c r="O66" s="85">
+      <c r="O66" s="90">
         <v>15</v>
       </c>
-      <c r="P66" s="85">
+      <c r="P66" s="90">
         <v>15</v>
       </c>
-      <c r="Q66" s="85">
+      <c r="Q66" s="90">
         <v>15</v>
       </c>
-      <c r="R66" s="85">
+      <c r="R66" s="90">
         <v>15</v>
       </c>
-      <c r="S66" s="85">
-        <v>0</v>
-      </c>
-      <c r="T66" s="85">
+      <c r="S66" s="90">
+        <v>0</v>
+      </c>
+      <c r="T66" s="90">
         <v>15</v>
       </c>
-      <c r="U66" s="85">
+      <c r="U66" s="90">
         <v>15</v>
       </c>
-      <c r="V66" s="85">
+      <c r="V66" s="90">
         <v>15</v>
       </c>
-      <c r="Y66" s="59"/>
-      <c r="Z66" s="59"/>
-      <c r="AA66" s="59"/>
-      <c r="AB66" s="59"/>
+      <c r="Y66" s="64"/>
+      <c r="Z66" s="64"/>
+      <c r="AA66" s="64"/>
+      <c r="AB66" s="64"/>
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="3:28">
-      <c r="C67" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="84">
+      <c r="C67" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D67" s="89">
         <f t="shared" ref="D67:V67" si="19">D66-D65</f>
         <v>-38</v>
       </c>
-      <c r="E67" s="84">
+      <c r="E67" s="89">
         <f t="shared" si="19"/>
         <v>126.5</v>
       </c>
-      <c r="F67" s="84">
+      <c r="F67" s="89">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="G67" s="84">
+      <c r="G67" s="89">
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="H67" s="84">
+      <c r="H67" s="89">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I67" s="84">
+      <c r="I67" s="89">
         <f t="shared" si="19"/>
         <v>-1</v>
       </c>
-      <c r="J67" s="84">
+      <c r="J67" s="89">
         <f t="shared" si="19"/>
         <v>-2</v>
       </c>
-      <c r="K67" s="84">
+      <c r="K67" s="89">
         <f t="shared" si="19"/>
         <v>-8</v>
       </c>
-      <c r="L67" s="84">
+      <c r="L67" s="89">
         <f t="shared" si="19"/>
         <v>-0.5</v>
       </c>
-      <c r="M67" s="84">
+      <c r="M67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="N67" s="84">
+      <c r="N67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="O67" s="84">
+      <c r="O67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="P67" s="84">
+      <c r="P67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="Q67" s="84">
+      <c r="Q67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="R67" s="84">
+      <c r="R67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="S67" s="84">
+      <c r="S67" s="89">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="T67" s="84">
+      <c r="T67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="U67" s="84">
+      <c r="U67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="V67" s="84">
+      <c r="V67" s="89">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="Y67" s="87"/>
-      <c r="Z67" s="88"/>
-      <c r="AA67" s="87"/>
-      <c r="AB67" s="87"/>
+      <c r="Y67" s="92"/>
+      <c r="Z67" s="93"/>
+      <c r="AA67" s="92"/>
+      <c r="AB67" s="92"/>
     </row>
     <row r="68" ht="18.75" customHeight="1"/>
     <row r="69" ht="18.75" customHeight="1"/>
@@ -6882,11 +6922,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="23">
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:W1"/>
-    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B7:C7"/>
@@ -6907,6 +6945,7 @@
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="Z19:AA20"/>
     <mergeCell ref="Z21:AA22"/>
+    <mergeCell ref="A1:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="expression" dxfId="0" priority="69">
